--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE194"/>
+  <dimension ref="A1:AE193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62471-2023</t>
+          <t>A 31484-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45268</v>
+        <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>11.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -894,151 +894,151 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Bårdlav
+Korallblylav
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 31484-2026 artfynd.xlsx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 31484-2026 karta.png", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 31484-2026 georefererad karta.tif", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 31484-2026 FSC-klagomål.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 31484-2026 FSC-klagomål mail.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 31484-2026 tillsynsbegäran.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 31484-2026 tillsynsbegäran mail.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 62471-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Kryddspindling
 Orange taggsvamp
 Zontaggsvamp</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 62471-2023 artfynd.xlsx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 62471-2023 karta.png", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 62471-2023 georefererad karta.tif", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 62471-2023 FSC-klagomål.docx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 62471-2023 FSC-klagomål mail.docx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 62471-2023 tillsynsbegäran.docx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 62471-2023 tillsynsbegäran mail.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 31484-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Bårdlav
-Korallblylav
-Rävticka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 31484-2026 artfynd.xlsx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 31484-2026 karta.png", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 31484-2026 georefererad karta.tif", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 31484-2026 FSC-klagomål.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 31484-2026 FSC-klagomål mail.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 31484-2026 tillsynsbegäran.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 31484-2026 tillsynsbegäran mail.docx", "A 31484-2026")</f>
         <v/>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55711-2024</t>
+          <t>A 15262-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45622</v>
+        <v>46105</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1218,480 +1218,480 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Brunklöver
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 63777-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 36009-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 55711-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45622</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Persiljespindling
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 15262-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>8</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63777-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46019</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 36009-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
         <v/>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 56936-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45773</v>
+        <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1943,19 +1943,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1989,42 +1984,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44873</v>
+        <v>45773</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,14 +2048,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2090,39 +2090,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         <v>45882</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45142</v>
+        <v>45744</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2270,20 +2270,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2298,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2310,46 +2310,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56936-2021</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2359,14 +2359,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44480</v>
+        <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2415,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2423,38 +2423,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45762</v>
+        <v>46139</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2483,19 +2483,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2522,49 +2517,53 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 28307-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2578,10 +2577,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46139</v>
+        <v>46196</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2593,14 +2592,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2634,46 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45744</v>
+        <v>45142</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2704,21 +2704,21 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2744,46 +2744,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28307-2026</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46196</v>
+        <v>46268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2854,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2862,38 +2862,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46268</v>
+        <v>46253</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,13 +2922,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2968,42 +2963,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>46253</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3033,13 +3028,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3073,42 +3068,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,10 +3117,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46253</v>
+        <v>45762</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3137,8 +3132,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3171,49 +3171,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46253</v>
+        <v>44873</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3283,35 +3283,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45737</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48544-2021</t>
+          <t>A 6353-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44452</v>
+        <v>44600</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6353-2022</t>
+          <t>A 47607-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44600</v>
+        <v>44852</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47607-2022</t>
+          <t>A 44015-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44852</v>
+        <v>44838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4093,8 +4093,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4137,7 +4142,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44015-2022</t>
+          <t>A 9875-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4151,10 +4156,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44838</v>
+        <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4166,13 +4171,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9875-2022</t>
+          <t>A 46641-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44620</v>
+        <v>44849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4244,8 +4244,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4288,7 +4293,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46641-2022</t>
+          <t>A 56929-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4298,14 +4303,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44849</v>
+        <v>44480</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4317,13 +4322,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56929-2021</t>
+          <t>A 42504-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4376,14 +4376,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44480</v>
+        <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4395,8 +4395,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4439,7 +4444,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42504-2022</t>
+          <t>A 42505-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4456,7 +4461,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4474,7 +4479,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4517,7 +4522,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42505-2022</t>
+          <t>A 12233-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4531,10 +4536,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44831</v>
+        <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4546,13 +4551,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12233-2022</t>
+          <t>A 67361-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44635</v>
+        <v>44523</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4685,7 +4685,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 67361-2021</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44523</v>
+        <v>45196</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4770,8 +4770,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4814,7 +4819,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4828,10 +4833,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45405</v>
+        <v>45607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4844,7 +4849,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4887,7 +4892,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4901,10 +4906,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44860</v>
+        <v>45699</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4917,7 +4922,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4960,7 +4965,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4974,10 +4979,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44523</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4990,7 +4995,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5033,7 +5038,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5047,10 +5052,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45474</v>
+        <v>44552</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5063,7 +5068,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5106,7 +5111,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5116,14 +5121,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45320</v>
+        <v>45792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5135,8 +5140,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>6.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5179,7 +5189,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5193,10 +5203,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45169</v>
+        <v>45792</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5210,11 +5220,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5257,7 +5267,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5271,10 +5281,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44973</v>
+        <v>45576</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5286,8 +5296,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5330,7 +5345,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5344,10 +5359,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45089</v>
+        <v>46006</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5360,7 +5375,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5403,7 +5418,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5413,14 +5428,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45056</v>
+        <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5433,7 +5448,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5476,7 +5491,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5490,10 +5505,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45408</v>
+        <v>45363</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5505,13 +5520,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>8.800000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5554,7 +5564,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5564,14 +5574,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45154</v>
+        <v>45274</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5584,7 +5594,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5627,7 +5637,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5641,10 +5651,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45405</v>
+        <v>45155</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5656,8 +5666,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5700,7 +5715,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5710,14 +5725,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45825</v>
+        <v>45154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5730,7 +5745,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5773,7 +5788,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5787,10 +5802,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45155</v>
+        <v>46014</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5802,13 +5817,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5851,7 +5861,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5865,10 +5875,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45827</v>
+        <v>46014</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5880,13 +5890,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>22.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5929,7 +5934,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5939,14 +5944,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45994</v>
+        <v>46020</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5958,13 +5963,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6007,7 +6007,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44973</v>
+        <v>45226</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6038,11 +6038,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6085,7 +6085,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45613</v>
+        <v>45705</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45607</v>
+        <v>45200</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6187,8 +6187,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6231,7 +6236,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6245,10 +6250,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45363</v>
+        <v>45567</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6261,7 +6266,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6304,7 +6309,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6318,10 +6323,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45918</v>
+        <v>45825</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6334,7 +6339,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6377,7 +6382,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45882</v>
+        <v>45827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6412,7 +6417,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6455,7 +6460,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6469,10 +6474,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45882</v>
+        <v>46045</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6484,13 +6489,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6533,7 +6533,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45937</v>
+        <v>45918</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6606,7 +6606,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6620,10 +6620,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45937</v>
+        <v>45730</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6679,7 +6679,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45631</v>
+        <v>45994</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6708,8 +6708,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6752,7 +6757,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6766,10 +6771,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46093</v>
+        <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6782,7 +6787,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6825,7 +6830,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6839,10 +6844,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46093</v>
+        <v>45937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6855,7 +6860,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6898,7 +6903,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6912,10 +6917,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45169</v>
+        <v>45316</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6927,13 +6932,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6976,7 +6976,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46099</v>
+        <v>45882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7007,11 +7007,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>15</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45705</v>
+        <v>45882</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7083,8 +7083,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7127,7 +7132,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7137,14 +7142,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44552</v>
+        <v>45274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7157,7 +7162,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7200,7 +7205,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7214,10 +7219,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46105</v>
+        <v>45179</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7229,8 +7234,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7273,7 +7283,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7287,10 +7297,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46105</v>
+        <v>45586</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7303,7 +7313,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7346,7 +7356,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7360,10 +7370,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46105</v>
+        <v>44691</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7377,11 +7387,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7424,7 +7434,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7438,10 +7448,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46108</v>
+        <v>45001</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7453,13 +7463,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>22.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7502,7 +7507,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7516,10 +7521,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45155</v>
+        <v>46093</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,13 +7536,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45966</v>
+        <v>46093</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7653,7 +7653,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46111</v>
+        <v>46099</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7731,7 +7731,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46113</v>
+        <v>44628</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7760,13 +7760,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7809,7 +7804,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7823,10 +7818,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45200</v>
+        <v>46105</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7838,13 +7833,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7887,7 +7877,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7901,10 +7891,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46114</v>
+        <v>46105</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7916,13 +7906,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7965,7 +7950,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7979,10 +7964,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46119</v>
+        <v>46105</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8000,7 +7985,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8043,7 +8028,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8057,10 +8042,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45978</v>
+        <v>46108</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8074,7 +8059,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -8121,7 +8106,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8135,10 +8120,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45764</v>
+        <v>46111</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8156,7 +8141,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8199,7 +8184,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8213,10 +8198,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45474</v>
+        <v>46114</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8228,8 +8213,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8272,7 +8262,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8286,10 +8276,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45989</v>
+        <v>46113</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8301,8 +8291,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8345,7 +8340,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8359,10 +8354,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45964</v>
+        <v>46119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8374,8 +8369,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8418,7 +8418,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46006</v>
+        <v>45729</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8491,7 +8491,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45103</v>
+        <v>45966</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8564,7 +8564,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45537</v>
+        <v>45405</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8637,7 +8637,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8651,10 +8651,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46008</v>
+        <v>45769</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8666,8 +8666,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8710,7 +8715,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8724,10 +8729,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46014</v>
+        <v>45978</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8739,8 +8744,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>22.8</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8783,7 +8793,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8793,14 +8803,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46014</v>
+        <v>44480</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8813,7 +8823,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8856,7 +8866,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8870,10 +8880,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46020</v>
+        <v>45554</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8929,7 +8939,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8943,10 +8953,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44852</v>
+        <v>45169</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8958,8 +8968,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9002,7 +9017,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9016,10 +9031,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45191</v>
+        <v>44860</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9031,13 +9046,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9080,7 +9090,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9094,10 +9104,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45089</v>
+        <v>45989</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9110,7 +9120,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9153,7 +9163,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9163,14 +9173,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44480</v>
+        <v>45964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9183,7 +9193,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9226,7 +9236,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9240,10 +9250,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45554</v>
+        <v>45232</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9255,8 +9265,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9299,7 +9314,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9313,10 +9328,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45169</v>
+        <v>45598</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9334,7 +9349,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9377,7 +9392,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9391,10 +9406,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44992</v>
+        <v>45679</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9407,7 +9422,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9450,7 +9465,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9464,10 +9479,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46045</v>
+        <v>45631</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9480,7 +9495,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9523,7 +9538,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9537,10 +9552,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45598</v>
+        <v>44992</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9552,13 +9567,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9601,7 +9611,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9615,10 +9625,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45607</v>
+        <v>45205</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9630,8 +9640,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9674,7 +9689,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9684,14 +9699,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45588</v>
+        <v>46142</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9704,7 +9719,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9747,7 +9762,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9761,10 +9776,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45028</v>
+        <v>45191</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9776,8 +9791,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9820,7 +9840,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9834,10 +9854,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45567</v>
+        <v>46146</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9849,8 +9869,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>12.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9893,7 +9918,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9907,10 +9932,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45063</v>
+        <v>46148</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9923,7 +9948,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9966,7 +9991,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9976,14 +10001,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9996,7 +10021,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10039,7 +10064,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10053,10 +10078,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10068,13 +10093,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>12.1</v>
+        <v>2.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10117,7 +10137,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10131,10 +10151,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10146,8 +10166,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10190,7 +10215,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10204,10 +10229,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10219,8 +10244,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10263,7 +10293,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10277,10 +10307,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46149</v>
+        <v>45597</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10293,7 +10323,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10336,7 +10366,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10346,14 +10376,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45205</v>
+        <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10365,13 +10395,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10414,7 +10439,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10428,10 +10453,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46153</v>
+        <v>45537</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10443,13 +10468,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10492,7 +10512,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10506,10 +10526,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10523,11 +10543,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10570,7 +10590,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10584,10 +10604,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45121</v>
+        <v>46189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10599,8 +10619,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>13.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10643,7 +10668,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10657,10 +10682,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44628</v>
+        <v>46189</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10672,8 +10697,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10716,7 +10746,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10730,10 +10760,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45440</v>
+        <v>46190</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10745,8 +10775,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10789,7 +10824,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10799,14 +10834,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45974</v>
+        <v>45103</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10819,7 +10854,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10862,7 +10897,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10872,14 +10907,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45196</v>
+        <v>46238</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10891,13 +10926,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10940,7 +10970,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10954,10 +10984,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45232</v>
+        <v>46153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10971,11 +11001,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11018,7 +11048,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11032,10 +11062,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45639</v>
+        <v>46246</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11048,7 +11078,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11091,7 +11121,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11105,10 +11135,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45408</v>
+        <v>46247</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11126,7 +11156,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11169,7 +11199,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11179,14 +11209,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45699</v>
+        <v>45607</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11199,7 +11229,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11242,7 +11272,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11256,10 +11286,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46176</v>
+        <v>45764</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11277,7 +11307,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11320,7 +11350,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11334,10 +11364,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45169</v>
+        <v>46258</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11355,7 +11385,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11398,7 +11428,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11412,10 +11442,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45155</v>
+        <v>46265</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11429,11 +11459,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11476,7 +11506,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11490,10 +11520,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45679</v>
+        <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11505,8 +11535,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11549,7 +11584,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11563,10 +11598,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45226</v>
+        <v>44852</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11578,13 +11613,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11627,7 +11657,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11641,10 +11671,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45730</v>
+        <v>46223</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11687,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11700,7 +11730,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11714,10 +11744,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46189</v>
+        <v>44973</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11729,13 +11759,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>13.7</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11778,7 +11803,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11792,10 +11817,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45049</v>
+        <v>46268</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11807,8 +11832,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11851,7 +11881,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11861,14 +11891,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46189</v>
+        <v>45320</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11880,13 +11910,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11929,7 +11954,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11943,10 +11968,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46190</v>
+        <v>46268</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11964,7 +11989,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.5</v>
+        <v>8.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12007,7 +12032,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12017,14 +12042,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46238</v>
+        <v>45454</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12037,7 +12062,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12080,7 +12105,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12094,10 +12119,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45631</v>
+        <v>45454</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12110,7 +12135,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12153,7 +12178,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12163,14 +12188,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45274</v>
+        <v>46197</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12182,8 +12207,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12226,7 +12256,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12240,10 +12270,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45769</v>
+        <v>46197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12257,11 +12287,11 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12304,7 +12334,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12318,10 +12348,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45769</v>
+        <v>46253</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12333,13 +12363,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12382,7 +12407,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12396,10 +12421,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45001</v>
+        <v>46266</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12411,8 +12436,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>22.4</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12455,7 +12485,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12469,10 +12499,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45607</v>
+        <v>46232</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12485,7 +12515,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12528,7 +12558,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12538,14 +12568,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45200</v>
+        <v>46232</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12559,11 +12589,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12606,7 +12636,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12616,14 +12646,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46153</v>
+        <v>45769</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12635,13 +12665,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12684,7 +12709,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12698,10 +12723,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46246</v>
+        <v>46233</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12713,8 +12738,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12757,7 +12787,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12771,10 +12801,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46247</v>
+        <v>45408</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12792,7 +12822,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12835,7 +12865,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12849,10 +12879,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45560</v>
+        <v>45056</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12864,13 +12894,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12913,7 +12938,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12927,10 +12952,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46258</v>
+        <v>45155</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12948,7 +12973,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12991,7 +13016,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13001,14 +13026,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
         <v>45056</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13021,7 +13046,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13064,7 +13089,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13078,10 +13103,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45233</v>
+        <v>45639</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13093,13 +13118,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13142,7 +13162,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13156,10 +13176,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45454</v>
+        <v>45474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13172,7 +13192,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13215,7 +13235,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13229,10 +13249,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45454</v>
+        <v>45588</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13245,7 +13265,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13288,7 +13308,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13302,10 +13322,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44727</v>
+        <v>44973</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13319,11 +13339,11 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.7</v>
+        <v>2.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13366,7 +13386,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13380,10 +13400,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45588</v>
+        <v>45034</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13395,8 +13415,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13439,7 +13464,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13453,10 +13478,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46265</v>
+        <v>45155</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13470,11 +13495,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13517,7 +13542,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13531,10 +13556,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46223</v>
+        <v>45474</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13547,7 +13572,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>9.800000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13590,7 +13615,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13604,10 +13629,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46265</v>
+        <v>45613</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13619,13 +13644,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13668,7 +13688,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13682,10 +13702,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45179</v>
+        <v>45408</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13703,7 +13723,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13746,7 +13766,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13760,10 +13780,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46268</v>
+        <v>45169</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13781,7 +13801,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.9</v>
+        <v>4.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13824,7 +13844,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13834,14 +13854,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45607</v>
+        <v>45560</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13853,8 +13873,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13897,7 +13922,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13907,14 +13932,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45769</v>
+        <v>45200</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13926,8 +13951,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13970,7 +14000,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13984,10 +14014,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46268</v>
+        <v>45769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14001,7 +14031,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -14048,7 +14078,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14062,10 +14092,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45316</v>
+        <v>45089</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14078,7 +14108,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14121,7 +14151,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14135,10 +14165,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45567</v>
+        <v>45588</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14151,7 +14181,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14211,7 +14241,7 @@
         <v>45632</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14272,7 +14302,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14286,10 +14316,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44691</v>
+        <v>45063</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14301,13 +14331,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14350,7 +14375,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14364,10 +14389,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45729</v>
+        <v>45607</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14380,7 +14405,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14423,7 +14448,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14437,10 +14462,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46197</v>
+        <v>45049</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14452,13 +14477,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14501,7 +14521,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14515,10 +14535,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46197</v>
+        <v>44523</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14530,13 +14550,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14579,7 +14594,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14593,10 +14608,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46253</v>
+        <v>45405</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14609,7 +14624,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14652,7 +14667,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14666,10 +14681,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45586</v>
+        <v>45233</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14681,8 +14696,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14725,7 +14745,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14739,10 +14759,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46266</v>
+        <v>45121</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14754,13 +14774,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14803,7 +14818,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14813,14 +14828,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46232</v>
+        <v>45028</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14832,13 +14847,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14881,7 +14891,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14895,10 +14905,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46233</v>
+        <v>45089</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14910,13 +14920,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14959,7 +14964,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14973,10 +14978,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45597</v>
+        <v>45567</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14989,7 +14994,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15032,7 +15037,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15046,10 +15051,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45034</v>
+        <v>44727</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15067,7 +15072,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15110,7 +15115,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15124,10 +15129,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44992</v>
+        <v>45607</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15140,7 +15145,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15183,7 +15188,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15197,10 +15202,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46232</v>
+        <v>44992</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15213,7 +15218,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15256,7 +15261,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15270,10 +15275,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45191</v>
+        <v>45169</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15287,11 +15292,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15334,7 +15339,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15348,10 +15353,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45196</v>
+        <v>45169</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15365,11 +15370,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15412,7 +15417,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15426,10 +15431,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45390</v>
+        <v>45440</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15442,7 +15447,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15485,7 +15490,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15499,10 +15504,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45792</v>
+        <v>45191</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15516,11 +15521,11 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15563,7 +15568,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15577,10 +15582,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45792</v>
+        <v>45196</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15594,11 +15599,11 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15641,7 +15646,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15655,10 +15660,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45274</v>
+        <v>45390</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15671,7 +15676,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15714,24 +15719,24 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>S 409-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45576</v>
+        <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15745,11 +15750,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>9.300000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15792,7 +15797,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S 409-2022</t>
+          <t>S 606-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15806,10 +15811,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44585</v>
+        <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15827,7 +15832,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>10.9</v>
+        <v>26.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15867,10 +15872,10 @@
       </c>
       <c r="V192" s="2" t="inlineStr"/>
     </row>
-    <row r="193" ht="15" customHeight="1">
+    <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S 606-2026</t>
+          <t>S 2097-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15880,14 +15885,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46085</v>
+        <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15899,13 +15904,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>26.4</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15944,79 +15944,6 @@
         <v>0</v>
       </c>
       <c r="V193" s="2" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>S 2097-2026</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D194" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E194" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I194" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J194" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" t="n">
-        <v>0</v>
-      </c>
-      <c r="O194" t="n">
-        <v>0</v>
-      </c>
-      <c r="P194" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="n">
-        <v>0</v>
-      </c>
-      <c r="T194" t="n">
-        <v>0</v>
-      </c>
-      <c r="U194" t="n">
-        <v>0</v>
-      </c>
-      <c r="V194" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31484-2026</t>
+          <t>A 62471-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46223</v>
+        <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11.7</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -894,151 +894,151 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Kryddspindling
+Orange taggsvamp
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 62471-2023 artfynd.xlsx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 62471-2023 karta.png", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 62471-2023 georefererad karta.tif", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 62471-2023 FSC-klagomål.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 62471-2023 FSC-klagomål mail.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 62471-2023 tillsynsbegäran.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 62471-2023 tillsynsbegäran mail.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31484-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Bårdlav
 Korallblylav
 Rävticka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 31484-2026 artfynd.xlsx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 31484-2026 karta.png", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 31484-2026 georefererad karta.tif", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 31484-2026 FSC-klagomål.docx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 31484-2026 FSC-klagomål mail.docx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 31484-2026 tillsynsbegäran.docx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 31484-2026 tillsynsbegäran mail.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 62471-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45268</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Kryddspindling
-Orange taggsvamp
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 62471-2023 artfynd.xlsx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 62471-2023 karta.png", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 62471-2023 georefererad karta.tif", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 62471-2023 FSC-klagomål.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 62471-2023 FSC-klagomål mail.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 62471-2023 tillsynsbegäran.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 62471-2023 tillsynsbegäran mail.docx", "A 62471-2023")</f>
         <v/>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>46105</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63777-2025</t>
+          <t>A 26072-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46019</v>
+        <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,42 +1336,42 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26072-2023</t>
+          <t>A 63777-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45091</v>
+        <v>46019</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1446,42 +1446,42 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 36009-2026</t>
+          <t>A 55711-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46266</v>
+        <v>45622</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1510,22 +1510,17 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1540,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1552,146 +1547,151 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Persiljespindling
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 36009-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Gullviva</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 55711-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45622</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Persiljespindling
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
         <v/>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56936-2021</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44480</v>
+        <v>45773</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1943,14 +1943,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1984,42 +1989,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2033,10 +2038,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45773</v>
+        <v>45882</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2050,38 +2055,38 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>15.5</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2090,46 +2095,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45882</v>
+        <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,14 +2165,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>15.5</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2179,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2188,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2204,42 +2209,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2258,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45744</v>
+        <v>44873</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2268,13 +2273,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2318,38 +2318,38 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45644</v>
+        <v>46139</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2415,46 +2415,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2468,10 +2472,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46139</v>
+        <v>45142</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2483,18 +2487,23 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2508,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2524,46 +2533,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28307-2026</t>
+          <t>A 56936-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2573,14 +2578,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46196</v>
+        <v>44480</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2590,11 +2595,6 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2604,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2638,42 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45142</v>
+        <v>45762</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2704,20 +2704,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2741,49 +2741,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 28307-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46268</v>
+        <v>46196</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2854,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2862,38 +2862,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46253</v>
+        <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2963,42 +2963,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,8 +3027,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3068,42 +3073,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3117,10 +3122,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45762</v>
+        <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,13 +3137,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3171,49 +3171,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44873</v>
+        <v>46253</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3283,35 +3283,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45737</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44600</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44852</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44480</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12233-2022</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44635</v>
+        <v>44860</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 67361-2021</t>
+          <t>A 12233-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44523</v>
+        <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2312-2022</t>
+          <t>A 67361-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4678,14 +4678,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44578</v>
+        <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4741,7 +4741,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 2312-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45196</v>
+        <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4770,13 +4770,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4819,7 +4814,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4833,10 +4828,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45607</v>
+        <v>45699</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4849,7 +4844,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4892,7 +4887,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4906,10 +4901,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45699</v>
+        <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4921,8 +4916,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44552</v>
+        <v>45405</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45792</v>
+        <v>45882</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45792</v>
+        <v>45882</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45576</v>
+        <v>45474</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5296,13 +5296,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>9.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5345,7 +5340,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46006</v>
+        <v>45155</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5374,8 +5369,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5418,7 +5418,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46008</v>
+        <v>45679</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5491,7 +5491,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45363</v>
+        <v>45226</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5520,8 +5520,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5564,7 +5569,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5578,10 +5583,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45274</v>
+        <v>45730</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5594,7 +5599,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5637,7 +5642,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45155</v>
+        <v>45049</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5666,13 +5671,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5715,7 +5715,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45154</v>
+        <v>45320</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5788,7 +5788,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5798,14 +5798,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46014</v>
+        <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5875,10 +5875,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46014</v>
+        <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5890,8 +5890,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>22.8</v>
+        <v>5.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5934,7 +5939,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5948,10 +5953,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46020</v>
+        <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6007,7 +6012,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6021,10 +6026,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45226</v>
+        <v>46093</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6036,13 +6041,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6085,7 +6085,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45705</v>
+        <v>46093</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45200</v>
+        <v>46099</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45567</v>
+        <v>45089</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45825</v>
+        <v>46105</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45827</v>
+        <v>46105</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6411,13 +6411,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6460,7 +6455,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6474,10 +6469,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46045</v>
+        <v>46105</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6489,8 +6484,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6533,7 +6533,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45918</v>
+        <v>45056</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6606,7 +6606,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6620,10 +6620,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45730</v>
+        <v>46108</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6635,8 +6635,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6679,7 +6684,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6689,14 +6694,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45994</v>
+        <v>45918</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6708,13 +6713,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45937</v>
+        <v>46111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6786,8 +6786,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6830,7 +6835,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6844,10 +6849,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45937</v>
+        <v>45408</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6859,8 +6864,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6903,7 +6913,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6917,10 +6927,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45316</v>
+        <v>46113</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6932,8 +6942,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6976,7 +6991,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6990,10 +7005,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45882</v>
+        <v>45631</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7005,13 +7020,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>15</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7054,7 +7064,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7068,10 +7078,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45882</v>
+        <v>46114</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7085,11 +7095,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7132,7 +7142,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7142,14 +7152,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45274</v>
+        <v>46119</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7161,8 +7171,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7205,7 +7220,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7215,14 +7230,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45179</v>
+        <v>45274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7234,13 +7249,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7283,7 +7293,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7297,10 +7307,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45586</v>
+        <v>45405</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7313,7 +7323,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.3</v>
+        <v>7.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7356,7 +7366,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7370,10 +7380,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44691</v>
+        <v>45155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7387,11 +7397,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7434,7 +7444,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7448,10 +7458,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45001</v>
+        <v>45769</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7463,8 +7473,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7507,7 +7522,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7521,10 +7536,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46093</v>
+        <v>45769</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7536,8 +7551,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7580,7 +7600,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7594,10 +7614,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46093</v>
+        <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7610,7 +7630,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7653,7 +7673,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7667,10 +7687,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46099</v>
+        <v>45937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7682,13 +7702,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7731,7 +7746,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7745,10 +7760,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44628</v>
+        <v>44973</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7760,8 +7775,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7804,7 +7824,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7818,10 +7838,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46105</v>
+        <v>45613</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7834,7 +7854,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7877,7 +7897,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7891,10 +7911,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46105</v>
+        <v>45607</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7907,7 +7927,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7950,7 +7970,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7964,10 +7984,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46105</v>
+        <v>45363</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7979,13 +7999,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8028,7 +8043,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8038,14 +8053,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46108</v>
+        <v>44480</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8057,13 +8072,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8106,7 +8116,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8120,10 +8130,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46111</v>
+        <v>45554</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8135,13 +8145,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8184,7 +8189,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8198,10 +8203,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46114</v>
+        <v>45966</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8213,13 +8218,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8262,7 +8262,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46113</v>
+        <v>45001</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8291,13 +8291,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>7</v>
+        <v>22.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8340,7 +8335,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8354,10 +8349,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46119</v>
+        <v>45169</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8375,7 +8370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8418,7 +8413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8432,10 +8427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45729</v>
+        <v>45598</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8447,8 +8442,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8491,7 +8491,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8520,8 +8520,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8564,7 +8569,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8578,10 +8583,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45405</v>
+        <v>45607</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8594,7 +8599,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8637,7 +8642,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8651,10 +8656,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45769</v>
+        <v>45200</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8668,11 +8673,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8715,7 +8720,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8729,10 +8734,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45978</v>
+        <v>45631</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8744,13 +8749,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8793,7 +8793,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8803,14 +8803,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44480</v>
+        <v>45989</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8876,14 +8876,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45554</v>
+        <v>46142</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8939,7 +8939,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45169</v>
+        <v>45964</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8968,13 +8968,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9017,7 +9012,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9031,10 +9026,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44860</v>
+        <v>45169</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9046,8 +9041,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9090,7 +9090,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45989</v>
+        <v>46146</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9119,8 +9119,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>12.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9163,7 +9168,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9177,10 +9182,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45964</v>
+        <v>46148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9193,7 +9198,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9236,7 +9241,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9250,10 +9255,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45232</v>
+        <v>46148</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9265,13 +9270,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9314,7 +9314,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45598</v>
+        <v>46149</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9343,13 +9343,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9392,7 +9387,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9406,10 +9401,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45679</v>
+        <v>45705</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9422,7 +9417,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9465,7 +9460,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9479,10 +9474,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45631</v>
+        <v>46153</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9494,8 +9489,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9538,7 +9538,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44992</v>
+        <v>44552</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9611,7 +9611,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45205</v>
+        <v>46006</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9640,13 +9640,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9689,7 +9684,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9699,14 +9694,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9718,8 +9713,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45191</v>
+        <v>45155</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9793,11 +9793,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46146</v>
+        <v>46008</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9869,13 +9869,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>12.1</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9918,7 +9913,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9932,10 +9927,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46148</v>
+        <v>46014</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9948,7 +9943,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.8</v>
+        <v>22.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9991,7 +9986,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10005,10 +10000,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46148</v>
+        <v>46014</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10021,7 +10016,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10064,7 +10059,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10078,10 +10073,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46149</v>
+        <v>45200</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10093,8 +10088,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46153</v>
+        <v>46020</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10166,13 +10166,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10215,7 +10210,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10225,14 +10220,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46153</v>
+        <v>45974</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10244,13 +10239,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10293,7 +10283,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10307,10 +10297,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45597</v>
+        <v>45764</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10322,8 +10312,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10366,7 +10361,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10376,14 +10371,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45974</v>
+        <v>45474</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10396,7 +10391,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10439,7 +10434,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10453,10 +10448,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45537</v>
+        <v>45560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10468,8 +10463,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10512,7 +10512,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46176</v>
+        <v>46045</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10541,13 +10541,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10590,7 +10585,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10604,10 +10599,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46189</v>
+        <v>46176</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10625,7 +10620,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>13.7</v>
+        <v>7.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10668,7 +10663,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10682,10 +10677,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46189</v>
+        <v>45103</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10697,13 +10692,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10746,7 +10736,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10760,10 +10750,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46190</v>
+        <v>45537</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10775,13 +10765,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10824,7 +10809,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10838,10 +10823,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45103</v>
+        <v>44852</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10854,7 +10839,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10897,7 +10882,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10907,14 +10892,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46238</v>
+        <v>45191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10926,8 +10911,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10970,7 +10960,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10984,10 +10974,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46153</v>
+        <v>45089</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10999,13 +10989,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11048,7 +11033,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11058,14 +11043,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46246</v>
+        <v>45994</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11077,8 +11062,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11121,7 +11111,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11135,10 +11125,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46247</v>
+        <v>46189</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11156,7 +11146,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.6</v>
+        <v>13.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11199,7 +11189,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11209,14 +11199,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45607</v>
+        <v>46189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11228,8 +11218,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11272,7 +11267,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11286,10 +11281,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45764</v>
+        <v>44992</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11301,13 +11296,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11350,7 +11340,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11364,10 +11354,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46258</v>
+        <v>46190</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11385,7 +11375,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11428,7 +11418,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11442,10 +11432,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46265</v>
+        <v>45607</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11457,13 +11447,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11506,7 +11491,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11520,10 +11505,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46265</v>
+        <v>45056</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11535,13 +11520,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11584,7 +11564,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11598,10 +11578,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44852</v>
+        <v>45233</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11611,6 +11591,11 @@
       <c r="G136" t="inlineStr">
         <is>
           <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -11657,7 +11642,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11671,10 +11656,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46223</v>
+        <v>45454</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11687,7 +11672,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11730,7 +11715,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11744,10 +11729,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44973</v>
+        <v>45454</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11760,7 +11745,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11803,7 +11788,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11817,10 +11802,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46268</v>
+        <v>45588</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11832,13 +11817,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11881,7 +11861,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11891,14 +11871,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45320</v>
+        <v>45028</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11911,7 +11891,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11954,7 +11934,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11968,10 +11948,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46268</v>
+        <v>45567</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11983,13 +11963,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>8.9</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12032,7 +12007,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12046,10 +12021,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45454</v>
+        <v>45063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12062,7 +12037,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12105,7 +12080,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12119,10 +12094,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45454</v>
+        <v>46153</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12134,8 +12109,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12178,7 +12158,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12192,10 +12172,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46197</v>
+        <v>46246</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12207,13 +12187,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12256,7 +12231,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12270,10 +12245,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46197</v>
+        <v>46247</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12291,7 +12266,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12334,7 +12309,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12348,10 +12323,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46253</v>
+        <v>44727</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12363,8 +12338,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>6.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12407,7 +12387,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12421,10 +12401,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46266</v>
+        <v>45205</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12442,7 +12422,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12485,7 +12465,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12499,10 +12479,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46232</v>
+        <v>45121</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12558,7 +12538,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12568,14 +12548,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46232</v>
+        <v>45588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12587,13 +12567,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12636,7 +12611,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12646,14 +12621,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45769</v>
+        <v>44628</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12666,7 +12641,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12709,7 +12684,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12723,10 +12698,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46233</v>
+        <v>45440</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12738,13 +12713,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12787,7 +12757,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12801,10 +12771,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45408</v>
+        <v>46258</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12822,7 +12792,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12865,7 +12835,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12879,10 +12849,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45056</v>
+        <v>45196</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12894,8 +12864,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12938,7 +12913,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12952,10 +12927,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45155</v>
+        <v>45232</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12973,7 +12948,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13016,7 +12991,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13026,14 +13001,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45056</v>
+        <v>45179</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13045,8 +13020,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13106,7 +13086,7 @@
         <v>45639</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13162,7 +13142,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13172,14 +13152,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45474</v>
+        <v>45607</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13192,7 +13172,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13235,7 +13215,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13249,10 +13229,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13264,8 +13244,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13308,7 +13293,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13318,14 +13303,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44973</v>
+        <v>45769</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13337,13 +13322,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13386,7 +13366,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13400,10 +13380,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45034</v>
+        <v>46265</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13417,11 +13397,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.1</v>
+        <v>3.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13464,7 +13444,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13478,10 +13458,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45155</v>
+        <v>46223</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13493,13 +13473,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13542,7 +13517,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13556,10 +13531,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45474</v>
+        <v>46265</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13571,8 +13546,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13615,7 +13595,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13629,10 +13609,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45613</v>
+        <v>46268</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13644,8 +13624,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.4</v>
+        <v>8.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13688,7 +13673,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13702,10 +13687,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45408</v>
+        <v>45316</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13717,13 +13702,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13766,7 +13746,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13780,10 +13760,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45169</v>
+        <v>46268</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13801,7 +13781,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13844,7 +13824,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13858,10 +13838,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45560</v>
+        <v>45567</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13873,13 +13853,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13922,7 +13897,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13936,10 +13911,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45200</v>
+        <v>45632</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13953,11 +13928,11 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14000,7 +13975,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14014,10 +13989,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45769</v>
+        <v>44691</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14035,7 +14010,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14078,7 +14053,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14092,10 +14067,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45089</v>
+        <v>45729</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14108,7 +14083,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14151,7 +14126,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14165,10 +14140,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45588</v>
+        <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14180,8 +14155,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14224,7 +14204,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14238,10 +14218,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45632</v>
+        <v>46197</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14255,11 +14235,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14302,7 +14282,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14316,10 +14296,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45063</v>
+        <v>46253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14332,7 +14312,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14375,7 +14355,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14389,10 +14369,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45607</v>
+        <v>45586</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14405,7 +14385,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14448,7 +14428,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14462,10 +14442,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45049</v>
+        <v>45597</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14478,7 +14458,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14521,7 +14501,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14535,10 +14515,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44523</v>
+        <v>45034</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14550,8 +14530,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14594,7 +14579,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14608,10 +14593,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45405</v>
+        <v>46266</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14623,8 +14608,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14667,7 +14657,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14677,14 +14667,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45233</v>
+        <v>46232</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14698,11 +14688,11 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14745,7 +14735,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14759,10 +14749,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45121</v>
+        <v>44992</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14775,7 +14765,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14818,7 +14808,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14832,10 +14822,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45028</v>
+        <v>46232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14848,7 +14838,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14891,7 +14881,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14905,10 +14895,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45089</v>
+        <v>45191</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14920,8 +14910,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14964,7 +14959,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14974,14 +14969,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45567</v>
+        <v>46238</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14994,7 +14989,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15037,7 +15032,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15051,10 +15046,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44727</v>
+        <v>45196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15072,7 +15067,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6.7</v>
+        <v>3.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15115,7 +15110,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15129,10 +15124,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45607</v>
+        <v>46233</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15144,8 +15139,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15202,10 +15202,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44992</v>
+        <v>45390</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15261,7 +15261,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15275,10 +15275,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45169</v>
+        <v>45792</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15292,11 +15292,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45169</v>
+        <v>45792</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15370,11 +15370,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15417,7 +15417,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15431,10 +15431,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45440</v>
+        <v>45274</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15490,7 +15490,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15504,10 +15504,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45191</v>
+        <v>45576</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15521,11 +15521,11 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15568,7 +15568,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45196</v>
+        <v>45825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15597,13 +15597,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15646,7 +15641,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15660,10 +15655,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45390</v>
+        <v>45827</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15675,8 +15670,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
         <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>46105</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26072-2023</t>
+          <t>A 63777-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45091</v>
+        <v>46019</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1336,42 +1336,42 @@
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 63777-2025</t>
+          <t>A 26072-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46019</v>
+        <v>45091</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1446,35 +1446,35 @@
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
         <v/>
       </c>
       <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
         <v/>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
         <v>45622</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 56936-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45773</v>
+        <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1943,19 +1943,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1989,42 +1984,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45882</v>
+        <v>45773</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2055,17 +2050,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2074,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2083,10 +2078,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2095,39 +2090,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
@@ -2151,7 +2146,7 @@
         <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2244,7 +2239,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2258,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44873</v>
+        <v>45882</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2273,24 +2268,29 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>15.5</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -2298,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2314,42 +2314,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46139</v>
+        <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2415,43 +2415,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
@@ -2475,7 +2471,7 @@
         <v>45142</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2564,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 56936-2021</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2578,14 +2574,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44480</v>
+        <v>46139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2594,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,35 +2634,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
         <v>45762</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>46196</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45644</v>
+        <v>44873</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2967,31 +2967,31 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
         <v>46268</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>46253</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45737</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44600</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44852</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44480</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 12233-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44860</v>
+        <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.8</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12233-2022</t>
+          <t>A 67361-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44635</v>
+        <v>44523</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 67361-2021</t>
+          <t>A 2312-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4678,14 +4678,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44523</v>
+        <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4741,7 +4741,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2312-2022</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44578</v>
+        <v>45196</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4770,8 +4770,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4831,7 +4836,7 @@
         <v>45699</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4887,7 +4892,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4901,10 +4906,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45169</v>
+        <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4916,13 +4921,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44523</v>
+        <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45405</v>
+        <v>44552</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45882</v>
+        <v>45155</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5142,11 +5142,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45882</v>
+        <v>45226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5220,11 +5220,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45474</v>
+        <v>45363</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5350,14 +5350,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45155</v>
+        <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5369,13 +5369,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>7.6</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5418,7 +5413,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5432,10 +5427,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45679</v>
+        <v>45705</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5448,7 +5443,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5491,7 +5486,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5505,10 +5500,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45226</v>
+        <v>45200</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5526,7 +5521,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5569,7 +5564,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5583,10 +5578,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45730</v>
+        <v>45274</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5599,7 +5594,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5642,7 +5637,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45049</v>
+        <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5672,7 +5667,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5715,7 +5710,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5725,14 +5720,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45320</v>
+        <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5745,7 +5740,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5788,7 +5783,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5798,14 +5793,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45154</v>
+        <v>45827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5817,8 +5812,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5875,10 +5875,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45169</v>
+        <v>45730</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5890,13 +5890,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5939,7 +5934,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5953,10 +5948,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44973</v>
+        <v>45918</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5969,7 +5964,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6012,7 +6007,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6026,10 +6021,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46093</v>
+        <v>45316</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6042,7 +6037,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6085,7 +6080,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6095,14 +6090,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46093</v>
+        <v>45274</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6115,7 +6110,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6158,7 +6153,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6172,10 +6167,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46099</v>
+        <v>45179</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6236,7 +6231,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6250,10 +6245,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45089</v>
+        <v>45586</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46105</v>
+        <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6339,7 +6334,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6382,7 +6377,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46105</v>
+        <v>46045</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6412,7 +6407,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6455,7 +6450,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6469,10 +6464,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46105</v>
+        <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6484,13 +6479,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6533,7 +6523,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6543,14 +6533,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45056</v>
+        <v>44691</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6562,8 +6552,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6606,7 +6601,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6620,10 +6615,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46108</v>
+        <v>45882</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6637,11 +6632,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>15</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6684,7 +6679,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6698,10 +6693,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45918</v>
+        <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6714,7 +6709,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>22.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6757,7 +6752,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6771,10 +6766,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46111</v>
+        <v>45882</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6788,11 +6783,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6835,7 +6830,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6849,10 +6844,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45408</v>
+        <v>44628</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6864,13 +6859,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6913,7 +6903,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6927,10 +6917,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46113</v>
+        <v>45729</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6942,13 +6932,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6991,7 +6976,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7005,10 +6990,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45631</v>
+        <v>45966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7021,7 +7006,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7064,7 +7049,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7078,10 +7063,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46114</v>
+        <v>45405</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,13 +7078,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7142,7 +7122,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7156,10 +7136,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46119</v>
+        <v>45769</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7173,11 +7153,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7220,7 +7200,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7234,10 +7214,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45274</v>
+        <v>45994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7249,8 +7229,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7293,7 +7278,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7307,10 +7292,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45405</v>
+        <v>45978</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7322,8 +7307,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7366,7 +7356,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7380,10 +7370,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45155</v>
+        <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7395,13 +7385,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7444,7 +7429,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7458,10 +7443,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45769</v>
+        <v>45989</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7473,13 +7458,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7522,7 +7502,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7536,10 +7516,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45769</v>
+        <v>45232</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7553,11 +7533,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7600,7 +7580,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7614,10 +7594,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45937</v>
+        <v>45964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7630,7 +7610,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7673,7 +7653,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7687,10 +7667,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45937</v>
+        <v>45679</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7703,7 +7683,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7746,7 +7726,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7760,10 +7740,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44973</v>
+        <v>45631</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7775,13 +7755,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7824,7 +7799,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7838,10 +7813,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45613</v>
+        <v>46006</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7854,7 +7829,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7897,7 +7872,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7911,10 +7886,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45607</v>
+        <v>44992</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7927,7 +7902,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7970,7 +7945,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7984,10 +7959,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45363</v>
+        <v>46008</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8000,7 +7975,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8043,7 +8018,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8053,14 +8028,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44480</v>
+        <v>45205</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8072,8 +8047,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8116,7 +8096,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8130,10 +8110,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45554</v>
+        <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8146,7 +8126,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8189,7 +8169,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8203,10 +8183,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45966</v>
+        <v>46014</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8219,7 +8199,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8262,7 +8242,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8276,10 +8256,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45001</v>
+        <v>46014</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8272,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8335,7 +8315,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8349,10 +8329,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45169</v>
+        <v>46093</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8364,13 +8344,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8413,7 +8388,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8427,10 +8402,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45598</v>
+        <v>46020</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8442,13 +8417,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8491,7 +8461,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8505,10 +8475,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45978</v>
+        <v>45191</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8522,11 +8492,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8569,7 +8539,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8583,10 +8553,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45607</v>
+        <v>46099</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8598,8 +8568,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8642,7 +8617,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8656,10 +8631,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45200</v>
+        <v>46105</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8671,13 +8646,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8720,7 +8690,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8734,10 +8704,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45631</v>
+        <v>46105</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8750,7 +8720,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8793,7 +8763,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8807,10 +8777,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45989</v>
+        <v>46105</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8822,8 +8792,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8866,7 +8841,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8876,14 +8851,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8895,8 +8870,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8939,7 +8919,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8953,10 +8933,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45964</v>
+        <v>45597</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8969,7 +8949,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9012,7 +8992,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9026,10 +9006,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45169</v>
+        <v>46111</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9047,7 +9027,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9090,7 +9070,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9104,10 +9084,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46146</v>
+        <v>46114</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9121,11 +9101,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>12.1</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9168,7 +9148,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9182,10 +9162,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46148</v>
+        <v>46113</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9197,8 +9177,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9241,7 +9226,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9255,10 +9240,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46148</v>
+        <v>46119</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9270,8 +9255,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9314,7 +9304,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9328,10 +9318,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46149</v>
+        <v>45537</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9344,7 +9334,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9387,7 +9377,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9401,10 +9391,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45705</v>
+        <v>45103</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9417,7 +9407,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9460,7 +9450,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9470,14 +9460,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46153</v>
+        <v>45607</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9489,13 +9479,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9538,7 +9523,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9548,14 +9533,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44552</v>
+        <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9568,7 +9553,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9611,7 +9596,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9625,10 +9610,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46006</v>
+        <v>45764</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9640,8 +9625,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9684,7 +9674,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9698,10 +9688,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46153</v>
+        <v>45554</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9713,13 +9703,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9762,7 +9747,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9776,10 +9761,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45155</v>
+        <v>45169</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9797,7 +9782,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9840,7 +9825,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9854,10 +9839,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46008</v>
+        <v>44852</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9870,7 +9855,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9913,7 +9898,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9927,10 +9912,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46014</v>
+        <v>45598</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9942,8 +9927,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>22.8</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9986,7 +9976,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10000,10 +9990,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46014</v>
+        <v>44973</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10016,7 +10006,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10059,7 +10049,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10069,14 +10059,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45200</v>
+        <v>45320</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10088,13 +10078,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10137,7 +10122,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10151,10 +10136,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46020</v>
+        <v>45454</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10167,7 +10152,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10210,7 +10195,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10220,14 +10205,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45974</v>
+        <v>45454</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10240,7 +10225,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10283,7 +10268,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10293,14 +10278,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45764</v>
+        <v>46142</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10312,13 +10297,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10361,7 +10341,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10371,14 +10351,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45474</v>
+        <v>45769</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10391,7 +10371,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10434,7 +10414,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10448,10 +10428,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45560</v>
+        <v>45408</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10465,11 +10445,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10512,7 +10492,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10526,10 +10506,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46045</v>
+        <v>46146</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10541,8 +10521,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>12.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10585,7 +10570,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10599,10 +10584,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46176</v>
+        <v>46148</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10614,13 +10599,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10663,7 +10643,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10677,10 +10657,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45103</v>
+        <v>46148</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10693,7 +10673,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10736,7 +10716,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10750,10 +10730,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45537</v>
+        <v>46149</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10766,7 +10746,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10809,7 +10789,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10823,10 +10803,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44852</v>
+        <v>45056</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10839,7 +10819,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10882,7 +10862,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10896,10 +10876,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45191</v>
+        <v>46153</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10917,7 +10897,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10960,7 +10940,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10974,10 +10954,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45089</v>
+        <v>46153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10987,6 +10967,11 @@
       <c r="G128" t="inlineStr">
         <is>
           <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -11033,7 +11018,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11043,14 +11028,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45994</v>
+        <v>45155</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11064,11 +11049,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11111,7 +11096,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11121,14 +11106,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46189</v>
+        <v>45056</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11140,13 +11125,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>13.7</v>
+        <v>5.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11189,7 +11169,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11203,10 +11183,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46189</v>
+        <v>45639</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11218,13 +11198,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11267,7 +11242,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11281,10 +11256,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44992</v>
+        <v>45474</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11297,7 +11272,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11340,7 +11315,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11354,10 +11329,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46190</v>
+        <v>45588</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11369,13 +11344,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11418,7 +11388,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11432,10 +11402,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45607</v>
+        <v>44973</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11447,8 +11417,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11491,7 +11466,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11501,14 +11476,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45056</v>
+        <v>45974</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11521,7 +11496,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11564,7 +11539,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11578,10 +11553,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45233</v>
+        <v>45034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11595,11 +11570,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11642,7 +11617,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11656,10 +11631,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45454</v>
+        <v>46176</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11671,8 +11646,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11715,7 +11695,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11729,10 +11709,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45454</v>
+        <v>45155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11744,8 +11724,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11788,7 +11773,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11802,10 +11787,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45588</v>
+        <v>45474</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11818,7 +11803,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11861,7 +11846,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11875,10 +11860,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45028</v>
+        <v>45613</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11891,7 +11876,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11934,7 +11919,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11948,10 +11933,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45567</v>
+        <v>46189</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11963,8 +11948,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>13.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12007,7 +11997,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12021,10 +12011,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45063</v>
+        <v>46189</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12036,8 +12026,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12080,7 +12075,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12094,10 +12089,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46153</v>
+        <v>46190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12111,11 +12106,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12158,7 +12153,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12172,10 +12167,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46246</v>
+        <v>45408</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12187,8 +12182,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12231,7 +12231,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12245,10 +12245,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46247</v>
+        <v>45169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12309,7 +12309,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12323,10 +12323,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44727</v>
+        <v>45560</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.7</v>
+        <v>3.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12387,7 +12387,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45205</v>
+        <v>45200</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12465,7 +12465,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12479,10 +12479,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45121</v>
+        <v>46153</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12494,8 +12494,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12538,7 +12543,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12552,10 +12557,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45588</v>
+        <v>45769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12567,8 +12572,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12611,7 +12621,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12625,10 +12635,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44628</v>
+        <v>45089</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12641,7 +12651,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12684,7 +12694,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12698,10 +12708,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45440</v>
+        <v>46246</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12714,7 +12724,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12757,7 +12767,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12771,10 +12781,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46258</v>
+        <v>45588</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12786,13 +12796,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12835,7 +12840,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12849,10 +12854,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45196</v>
+        <v>46247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12866,11 +12871,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12913,7 +12918,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12927,10 +12932,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45232</v>
+        <v>45632</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12944,11 +12949,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12991,7 +12996,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13005,10 +13010,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45179</v>
+        <v>45063</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13020,13 +13025,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13069,7 +13069,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45639</v>
+        <v>45607</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13152,14 +13152,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45607</v>
+        <v>45049</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13215,7 +13215,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45408</v>
+        <v>44523</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13242,11 +13242,6 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -13293,7 +13288,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13303,14 +13298,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45769</v>
+        <v>45405</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13323,7 +13318,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13366,7 +13361,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13380,10 +13375,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13401,7 +13396,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13444,7 +13439,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13458,10 +13453,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46223</v>
+        <v>45233</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13473,8 +13468,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13517,7 +13517,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46265</v>
+        <v>45121</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13546,13 +13546,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13595,7 +13590,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13609,10 +13604,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13630,7 +13625,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8.9</v>
+        <v>3.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13673,7 +13668,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13687,10 +13682,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45316</v>
+        <v>46265</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13702,8 +13697,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13746,7 +13746,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13760,10 +13760,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46268</v>
+        <v>45028</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13775,13 +13775,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13824,7 +13819,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13838,10 +13833,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45567</v>
+        <v>46223</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13854,7 +13849,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13897,7 +13892,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13911,10 +13906,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45632</v>
+        <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13926,13 +13921,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13975,7 +13965,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13989,10 +13979,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44691</v>
+        <v>46268</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14006,11 +13996,11 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14053,7 +14043,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14067,10 +14057,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45729</v>
+        <v>45567</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14083,7 +14073,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14126,7 +14116,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14140,10 +14130,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46197</v>
+        <v>46268</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14161,7 +14151,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14204,7 +14194,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14218,10 +14208,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46197</v>
+        <v>44727</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14235,11 +14225,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14282,7 +14272,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14296,10 +14286,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46253</v>
+        <v>46197</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14311,8 +14301,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14355,7 +14350,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14369,10 +14364,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45586</v>
+        <v>46197</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14384,8 +14379,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14428,7 +14428,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14442,10 +14442,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45597</v>
+        <v>45607</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14501,7 +14501,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14515,10 +14515,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45034</v>
+        <v>46253</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14530,13 +14530,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14579,7 +14574,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14593,10 +14588,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46266</v>
+        <v>44992</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14608,13 +14603,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14657,7 +14647,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14667,14 +14657,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46232</v>
+        <v>45169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14688,11 +14678,11 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14735,7 +14725,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14749,10 +14739,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44992</v>
+        <v>46266</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14764,8 +14754,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14825,7 +14820,7 @@
         <v>46232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14881,7 +14876,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14895,10 +14890,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45191</v>
+        <v>45169</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14912,11 +14907,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14959,7 +14954,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14969,14 +14964,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14988,8 +14983,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15032,7 +15032,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15046,10 +15046,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45196</v>
+        <v>46233</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15063,11 +15063,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15110,7 +15110,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15124,10 +15124,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46233</v>
+        <v>45440</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15139,13 +15139,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15188,7 +15183,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15202,10 +15197,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45390</v>
+        <v>45191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15217,8 +15212,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15261,7 +15261,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15275,10 +15275,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45792</v>
+        <v>45196</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15292,11 +15292,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15349,14 +15349,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45792</v>
+        <v>46238</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15368,13 +15368,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15417,7 +15412,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15431,10 +15426,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45274</v>
+        <v>45390</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15447,7 +15442,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15490,7 +15485,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15504,10 +15499,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45576</v>
+        <v>45792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15525,7 +15520,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>9.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15568,7 +15563,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15582,10 +15577,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45825</v>
+        <v>45792</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15597,8 +15592,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15641,7 +15641,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45827</v>
+        <v>45576</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
         <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15262-2026</t>
+          <t>A 55711-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46105</v>
+        <v>45622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1218,369 +1218,369 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Persiljespindling
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 15262-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Brunklöver
 Tvåblad</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 63777-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46019</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>3.4</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>8</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>8</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63777-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>8</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>8</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55711-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45622</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Persiljespindling
-Skogsknipprot</t>
-        </is>
-      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56936-2021</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44480</v>
+        <v>45773</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1943,14 +1943,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1984,42 +1989,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2033,10 +2038,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45773</v>
+        <v>44873</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2048,19 +2053,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2090,46 +2090,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45744</v>
+        <v>45882</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,27 +2160,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>15.5</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
@@ -2188,10 +2188,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2204,42 +2204,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45882</v>
+        <v>45142</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2270,11 +2270,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>15.5</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2283,13 +2283,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,46 +2310,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 56936-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2359,14 +2359,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45644</v>
+        <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2415,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2423,38 +2423,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45142</v>
+        <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,20 +2485,20 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2522,42 +2522,42 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
         <v>46139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 28307-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45762</v>
+        <v>46196</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2741,49 +2741,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28307-2026</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46196</v>
+        <v>45744</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2854,46 +2854,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44873</v>
+        <v>46268</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,14 +2922,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2963,42 +2968,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46268</v>
+        <v>46253</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,13 +3032,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3073,42 +3073,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3125,7 +3125,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3182,38 +3182,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46253</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3283,35 +3283,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45737</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44600</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44852</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44480</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 67361-2021</t>
+          <t>A 2312-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44523</v>
+        <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2312-2022</t>
+          <t>A 67361-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4678,14 +4678,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44578</v>
+        <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4741,7 +4741,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45196</v>
+        <v>45405</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4770,13 +4770,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4819,7 +4814,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4833,10 +4828,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45699</v>
+        <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4849,7 +4844,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4892,7 +4887,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4906,10 +4901,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45631</v>
+        <v>44860</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4922,7 +4917,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4965,7 +4960,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4979,10 +4974,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45607</v>
+        <v>45474</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4995,7 +4990,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5038,7 +5033,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5048,14 +5043,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44552</v>
+        <v>45320</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5068,7 +5063,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5111,7 +5106,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5121,14 +5116,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45155</v>
+        <v>45154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5140,13 +5135,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5189,7 +5179,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5203,10 +5193,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45226</v>
+        <v>45169</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5224,7 +5214,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5267,7 +5257,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5281,10 +5271,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45363</v>
+        <v>44973</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5297,7 +5287,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5340,7 +5330,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5350,14 +5340,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45154</v>
+        <v>45089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5370,7 +5360,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5413,7 +5403,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5423,14 +5413,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45705</v>
+        <v>45056</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5443,7 +5433,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5486,7 +5476,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5500,10 +5490,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45200</v>
+        <v>45408</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5521,7 +5511,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5564,7 +5554,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5578,10 +5568,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45274</v>
+        <v>45405</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5594,7 +5584,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5637,7 +5627,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5647,14 +5637,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45567</v>
+        <v>45994</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5666,8 +5656,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5727,7 +5722,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5783,7 +5778,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5797,10 +5792,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45827</v>
+        <v>45155</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5814,11 +5809,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5861,7 +5856,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5875,10 +5870,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45730</v>
+        <v>45827</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5890,8 +5885,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5934,7 +5934,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45918</v>
+        <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5963,8 +5963,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6007,7 +6012,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6021,10 +6026,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45316</v>
+        <v>46093</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6037,7 +6042,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6080,7 +6085,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6090,14 +6095,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45274</v>
+        <v>46093</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6110,7 +6115,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6153,7 +6158,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6167,10 +6172,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45179</v>
+        <v>45613</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6182,13 +6187,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6231,7 +6231,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45586</v>
+        <v>46099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6260,8 +6260,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6304,7 +6309,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6318,10 +6323,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45937</v>
+        <v>45607</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6334,7 +6339,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6377,7 +6382,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46045</v>
+        <v>45363</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6407,7 +6412,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6450,7 +6455,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6464,10 +6469,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45937</v>
+        <v>46105</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6480,7 +6485,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6523,7 +6528,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6537,10 +6542,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44691</v>
+        <v>46105</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6552,13 +6557,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45882</v>
+        <v>46105</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6632,11 +6632,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6679,7 +6679,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45001</v>
+        <v>46108</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6708,8 +6708,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>22.4</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6752,7 +6757,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6766,10 +6771,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45882</v>
+        <v>46111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6783,11 +6788,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6830,7 +6835,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6844,10 +6849,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44628</v>
+        <v>46113</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6859,8 +6864,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6903,7 +6913,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6917,10 +6927,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45729</v>
+        <v>46114</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6932,8 +6942,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6976,7 +6991,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6990,10 +7005,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45966</v>
+        <v>46119</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7005,8 +7020,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>6.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7049,7 +7069,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7063,10 +7083,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45405</v>
+        <v>45882</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7078,8 +7098,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7122,7 +7147,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7136,10 +7161,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45769</v>
+        <v>45882</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7157,7 +7182,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7200,7 +7225,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7210,14 +7235,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45994</v>
+        <v>45631</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7229,13 +7254,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7278,7 +7298,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7292,10 +7312,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45978</v>
+        <v>45169</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7309,11 +7329,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7356,7 +7376,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7370,10 +7390,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44860</v>
+        <v>45705</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7386,7 +7406,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7429,7 +7449,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7443,10 +7463,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45989</v>
+        <v>44552</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7459,7 +7479,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7502,7 +7522,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7516,10 +7536,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45232</v>
+        <v>45918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,13 +7551,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7580,7 +7595,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7594,10 +7609,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45964</v>
+        <v>45155</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7609,8 +7624,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7653,7 +7673,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7663,14 +7683,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45679</v>
+        <v>44480</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7683,7 +7703,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7726,7 +7746,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7740,10 +7760,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45631</v>
+        <v>45554</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7756,7 +7776,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7799,7 +7819,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7813,10 +7833,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46006</v>
+        <v>45200</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7828,8 +7848,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7872,7 +7897,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7886,10 +7911,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44992</v>
+        <v>45169</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7901,8 +7926,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7945,7 +7975,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7959,10 +7989,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46008</v>
+        <v>45764</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7974,8 +8004,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8018,7 +8053,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8032,10 +8067,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45205</v>
+        <v>45598</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8053,7 +8088,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8096,7 +8131,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8110,10 +8145,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46093</v>
+        <v>45474</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8126,7 +8161,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8169,7 +8204,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8179,14 +8214,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8199,7 +8234,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8242,7 +8277,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8256,10 +8291,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46014</v>
+        <v>46146</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8271,8 +8306,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>22.8</v>
+        <v>12.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8315,7 +8355,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8329,10 +8369,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46093</v>
+        <v>46148</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8345,7 +8385,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8388,7 +8428,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8402,10 +8442,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46020</v>
+        <v>45103</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8418,7 +8458,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8461,7 +8501,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8475,10 +8515,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45191</v>
+        <v>46148</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8490,13 +8530,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8539,7 +8574,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8553,10 +8588,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46099</v>
+        <v>46149</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8568,13 +8603,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8617,7 +8647,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8631,10 +8661,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46105</v>
+        <v>45537</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8647,7 +8677,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8690,7 +8720,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8704,10 +8734,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46105</v>
+        <v>46153</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8719,8 +8749,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8763,7 +8798,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8777,10 +8812,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46105</v>
+        <v>46153</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8794,11 +8829,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8841,7 +8876,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8855,10 +8890,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46108</v>
+        <v>44852</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8870,13 +8905,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8919,7 +8949,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8933,10 +8963,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45597</v>
+        <v>45191</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8948,8 +8978,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8992,7 +9027,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9006,10 +9041,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46111</v>
+        <v>45089</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9021,13 +9056,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9070,7 +9100,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9084,10 +9114,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46114</v>
+        <v>45937</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9097,11 +9127,6 @@
       <c r="G103" t="inlineStr">
         <is>
           <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -9148,7 +9173,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9162,10 +9187,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46113</v>
+        <v>45937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9177,13 +9202,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9226,7 +9246,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9236,14 +9256,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46119</v>
+        <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9255,13 +9275,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9304,7 +9319,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9318,10 +9333,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45537</v>
+        <v>44992</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9334,7 +9349,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9377,7 +9392,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9391,10 +9406,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45103</v>
+        <v>45607</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9407,7 +9422,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9450,7 +9465,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9460,14 +9475,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45607</v>
+        <v>45588</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9480,7 +9495,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9523,7 +9538,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9533,14 +9548,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44480</v>
+        <v>45028</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9553,7 +9568,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9596,7 +9611,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9610,10 +9625,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45764</v>
+        <v>46176</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9631,7 +9646,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9674,7 +9689,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9688,10 +9703,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45554</v>
+        <v>45567</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9704,7 +9719,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9747,7 +9762,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9761,10 +9776,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45169</v>
+        <v>45063</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9776,13 +9791,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9825,7 +9835,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9839,10 +9849,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44852</v>
+        <v>46189</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9854,8 +9864,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>13.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9898,7 +9913,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9912,10 +9927,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45598</v>
+        <v>45205</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9933,7 +9948,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9976,7 +9991,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9990,10 +10005,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44973</v>
+        <v>46189</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10005,8 +10020,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10049,7 +10069,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10059,14 +10079,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45320</v>
+        <v>46190</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10078,8 +10098,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10122,7 +10147,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10136,10 +10161,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45454</v>
+        <v>45121</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10152,7 +10177,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10195,7 +10220,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10209,10 +10234,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45454</v>
+        <v>45966</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10225,7 +10250,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10268,7 +10293,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10278,14 +10303,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46142</v>
+        <v>44628</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10298,7 +10323,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10341,7 +10366,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10351,14 +10376,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45769</v>
+        <v>45440</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10371,7 +10396,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10414,7 +10439,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10428,10 +10453,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45408</v>
+        <v>45978</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10445,11 +10470,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10492,7 +10517,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10506,10 +10531,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46146</v>
+        <v>45196</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10527,7 +10552,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>12.1</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10570,7 +10595,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10584,10 +10609,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10599,8 +10624,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10643,7 +10673,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10657,10 +10687,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46148</v>
+        <v>46246</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10673,7 +10703,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10716,7 +10746,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10730,10 +10760,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46149</v>
+        <v>45232</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10745,8 +10775,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10789,7 +10824,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10803,10 +10838,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45056</v>
+        <v>46247</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10818,8 +10853,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10862,7 +10902,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10876,10 +10916,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46153</v>
+        <v>45639</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10891,13 +10931,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10940,7 +10975,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10954,10 +10989,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46153</v>
+        <v>45408</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10971,11 +11006,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11018,7 +11053,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11032,10 +11067,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45155</v>
+        <v>45699</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11047,13 +11082,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11096,7 +11126,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11106,14 +11136,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45056</v>
+        <v>45169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11125,8 +11155,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11169,7 +11204,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11183,10 +11218,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45639</v>
+        <v>45989</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11199,7 +11234,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11242,7 +11277,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11256,10 +11291,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45474</v>
+        <v>45155</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11271,8 +11306,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11315,7 +11355,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11329,10 +11369,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45588</v>
+        <v>45964</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11345,7 +11385,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11388,7 +11428,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11402,10 +11442,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44973</v>
+        <v>46258</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11419,11 +11459,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11466,7 +11506,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11476,14 +11516,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45974</v>
+        <v>45679</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11496,7 +11536,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11539,7 +11579,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11553,10 +11593,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45034</v>
+        <v>45226</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11570,11 +11610,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11617,7 +11657,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11631,10 +11671,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46176</v>
+        <v>45730</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11646,13 +11686,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11695,7 +11730,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11709,10 +11744,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45155</v>
+        <v>45049</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11724,13 +11759,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11773,7 +11803,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11787,10 +11817,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45474</v>
+        <v>46265</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11802,8 +11832,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11846,7 +11881,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11860,10 +11895,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45613</v>
+        <v>46223</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11876,7 +11911,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11919,7 +11954,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11933,10 +11968,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46189</v>
+        <v>46265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11954,7 +11989,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11997,7 +12032,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12011,10 +12046,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46189</v>
+        <v>46006</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12026,13 +12061,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12075,7 +12105,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12089,10 +12119,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46190</v>
+        <v>46268</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12110,7 +12140,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>8.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12153,7 +12183,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12167,10 +12197,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45408</v>
+        <v>46268</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12188,7 +12218,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12231,7 +12261,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12245,10 +12275,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45169</v>
+        <v>45631</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12260,13 +12290,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12309,7 +12334,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12323,10 +12348,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45560</v>
+        <v>46008</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12338,13 +12363,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12387,7 +12407,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12397,14 +12417,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45200</v>
+        <v>45274</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12416,13 +12436,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12465,7 +12480,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12479,10 +12494,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46153</v>
+        <v>46014</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12494,13 +12509,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>3.9</v>
+        <v>22.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12543,7 +12553,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12557,10 +12567,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45769</v>
+        <v>46014</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12572,13 +12582,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12621,7 +12626,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12635,10 +12640,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45089</v>
+        <v>46197</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12650,8 +12655,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12694,7 +12704,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12708,10 +12718,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46246</v>
+        <v>46197</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12723,8 +12733,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12767,7 +12782,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12781,10 +12796,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45588</v>
+        <v>46253</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12797,7 +12812,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12840,7 +12855,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12854,10 +12869,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46247</v>
+        <v>46020</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12869,13 +12884,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12918,7 +12928,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12932,10 +12942,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45632</v>
+        <v>45769</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12949,11 +12959,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12996,7 +13006,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13010,10 +13020,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45063</v>
+        <v>45769</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13025,8 +13035,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13069,7 +13084,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13083,10 +13098,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45607</v>
+        <v>46266</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13098,8 +13113,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13142,7 +13162,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13152,14 +13172,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45049</v>
+        <v>46232</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13171,8 +13191,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13215,7 +13240,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13229,10 +13254,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44523</v>
+        <v>46232</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13245,7 +13270,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13288,7 +13313,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13302,10 +13327,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45405</v>
+        <v>45001</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13318,7 +13343,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.7</v>
+        <v>22.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13361,7 +13386,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13375,10 +13400,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46258</v>
+        <v>46233</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13396,7 +13421,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13439,7 +13464,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13453,10 +13478,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45233</v>
+        <v>45607</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13468,13 +13493,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13517,7 +13537,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13531,10 +13551,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45121</v>
+        <v>45200</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13546,8 +13566,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13590,7 +13615,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13600,14 +13625,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46265</v>
+        <v>46238</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13619,13 +13644,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13668,7 +13688,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13682,10 +13702,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46265</v>
+        <v>45560</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13699,11 +13719,11 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13746,7 +13766,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13760,10 +13780,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45028</v>
+        <v>46045</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13776,7 +13796,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13819,7 +13839,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13833,10 +13853,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46223</v>
+        <v>45056</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13849,7 +13869,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>9.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13892,7 +13912,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13906,10 +13926,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45089</v>
+        <v>45233</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13921,8 +13941,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13965,7 +13990,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13979,10 +14004,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46268</v>
+        <v>45454</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13994,13 +14019,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14043,7 +14063,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14057,10 +14077,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45567</v>
+        <v>45454</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14073,7 +14093,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14116,7 +14136,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14130,10 +14150,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46268</v>
+        <v>44727</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14147,11 +14167,11 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14194,7 +14214,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14208,10 +14228,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44727</v>
+        <v>45588</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14223,13 +14243,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14272,7 +14287,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14286,10 +14301,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46197</v>
+        <v>45179</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14307,7 +14322,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14350,7 +14365,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14360,14 +14375,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46197</v>
+        <v>45607</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14379,13 +14394,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14428,7 +14438,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14438,14 +14448,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45607</v>
+        <v>45769</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14458,7 +14468,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14501,7 +14511,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14515,10 +14525,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46253</v>
+        <v>45316</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14531,7 +14541,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14574,7 +14584,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14588,10 +14598,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44992</v>
+        <v>45567</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14604,7 +14614,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14647,7 +14657,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14661,10 +14671,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45169</v>
+        <v>45632</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14678,11 +14688,11 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14725,7 +14735,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14739,10 +14749,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46266</v>
+        <v>44691</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14756,11 +14766,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14803,7 +14813,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14817,10 +14827,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46232</v>
+        <v>45729</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14833,7 +14843,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14876,7 +14886,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14890,10 +14900,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45169</v>
+        <v>45586</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14905,13 +14915,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14954,7 +14959,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14964,14 +14969,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46232</v>
+        <v>45597</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14983,13 +14988,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15032,7 +15032,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15046,10 +15046,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46233</v>
+        <v>45034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15063,11 +15063,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15110,7 +15110,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15124,10 +15124,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45440</v>
+        <v>44992</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15200,7 +15200,7 @@
         <v>45191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45196</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15349,14 +15349,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46238</v>
+        <v>45390</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15412,7 +15412,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15426,10 +15426,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45390</v>
+        <v>45792</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15441,8 +15441,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15502,7 +15507,7 @@
         <v>45792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15563,7 +15568,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15577,10 +15582,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45792</v>
+        <v>45274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15592,13 +15597,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15658,7 +15658,7 @@
         <v>45576</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55711-2024</t>
+          <t>A 63777-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45622</v>
+        <v>46019</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1218,369 +1218,369 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 15262-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Brunklöver
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55711-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45622</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Persiljespindling
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 15262-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>8</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63777-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46019</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 56936-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45773</v>
+        <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1943,19 +1943,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1989,42 +1984,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44873</v>
+        <v>45773</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,14 +2048,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2090,46 +2090,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45882</v>
+        <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,14 +2160,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>15.5</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2188,10 +2188,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2204,42 +2204,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45142</v>
+        <v>45644</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2268,22 +2268,17 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2298,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2310,46 +2305,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56936-2021</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2359,14 +2354,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44480</v>
+        <v>46139</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,7 +2374,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2419,42 +2414,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2468,10 +2467,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45762</v>
+        <v>45142</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,35 +2484,35 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2522,49 +2521,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2578,10 +2577,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46139</v>
+        <v>45762</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2593,14 +2592,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2627,46 +2631,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
         <v>46196</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45744</v>
+        <v>44873</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,13 +2812,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2862,31 +2857,31 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
@@ -2910,7 +2905,7 @@
         <v>46268</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3015,7 @@
         <v>46253</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3120,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3208,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3222,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>45882</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3242,24 +3237,29 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>15.5</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -3267,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,35 +3283,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45737</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44600</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44852</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44480</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45405</v>
+        <v>45196</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4770,8 +4770,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4814,7 +4819,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4828,10 +4833,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44523</v>
+        <v>45699</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4844,7 +4849,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4887,7 +4892,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4901,10 +4906,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44860</v>
+        <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4917,7 +4922,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4960,7 +4965,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4974,10 +4979,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45474</v>
+        <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4990,7 +4995,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5033,7 +5038,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5043,14 +5048,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45320</v>
+        <v>44552</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5063,7 +5068,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5106,7 +5111,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5116,14 +5121,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5135,8 +5140,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5179,7 +5189,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5193,10 +5203,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45169</v>
+        <v>45363</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5208,13 +5218,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5257,7 +5262,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5271,10 +5276,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44973</v>
+        <v>45226</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5286,8 +5291,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5330,7 +5340,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5340,14 +5350,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45089</v>
+        <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5360,7 +5370,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5403,7 +5413,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5413,14 +5423,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45056</v>
+        <v>45705</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5433,7 +5443,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5476,7 +5486,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5490,10 +5500,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45408</v>
+        <v>45200</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5511,7 +5521,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5554,7 +5564,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5568,10 +5578,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45405</v>
+        <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5584,7 +5594,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5627,7 +5637,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5637,14 +5647,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45994</v>
+        <v>45730</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5656,13 +5666,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5705,7 +5710,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5719,10 +5724,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45825</v>
+        <v>45316</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5735,7 +5740,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5778,7 +5783,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5788,14 +5793,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45155</v>
+        <v>45274</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5807,13 +5812,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45827</v>
+        <v>45179</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5887,11 +5887,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5934,7 +5934,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44973</v>
+        <v>45586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5963,13 +5963,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6012,7 +6007,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6026,10 +6021,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46093</v>
+        <v>44691</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6041,8 +6036,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6085,7 +6085,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46093</v>
+        <v>45001</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>22.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45613</v>
+        <v>44628</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6231,7 +6231,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46099</v>
+        <v>45729</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6260,13 +6260,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45607</v>
+        <v>45405</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6339,7 +6334,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6382,7 +6377,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45363</v>
+        <v>45769</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6411,8 +6406,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46105</v>
+        <v>45554</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46105</v>
+        <v>45169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6557,8 +6557,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6601,7 +6606,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6615,10 +6620,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46105</v>
+        <v>44860</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6630,13 +6635,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6679,7 +6679,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46108</v>
+        <v>45598</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46111</v>
+        <v>45232</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6835,7 +6835,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46113</v>
+        <v>45679</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6864,13 +6864,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6913,7 +6908,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6927,10 +6922,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46114</v>
+        <v>45631</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6942,13 +6937,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6991,7 +6981,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7005,10 +6995,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46119</v>
+        <v>44992</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7020,13 +7010,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7069,7 +7054,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7083,10 +7068,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45882</v>
+        <v>45205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7100,11 +7085,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7147,7 +7132,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7161,10 +7146,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45882</v>
+        <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7176,13 +7161,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7225,7 +7205,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7239,10 +7219,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45631</v>
+        <v>45191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7254,8 +7234,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7298,7 +7283,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7308,14 +7293,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45169</v>
+        <v>46142</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7327,13 +7312,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7376,7 +7356,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7390,10 +7370,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45705</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7406,7 +7386,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7449,7 +7429,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7463,10 +7443,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44552</v>
+        <v>46146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7478,8 +7458,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>12.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7522,7 +7507,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7536,10 +7521,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45918</v>
+        <v>45597</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7552,7 +7537,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7595,7 +7580,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7609,10 +7594,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45155</v>
+        <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7624,13 +7609,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7673,7 +7653,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7683,14 +7663,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44480</v>
+        <v>46148</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7703,7 +7683,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7746,7 +7726,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7760,10 +7740,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45554</v>
+        <v>46148</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7776,7 +7756,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7819,7 +7799,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7833,10 +7813,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45200</v>
+        <v>45537</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7848,13 +7828,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7897,7 +7872,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7911,10 +7886,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45169</v>
+        <v>46149</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7926,13 +7901,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7975,7 +7945,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7989,10 +7959,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45764</v>
+        <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8004,13 +7974,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8053,7 +8018,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8067,10 +8032,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45598</v>
+        <v>46153</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8084,11 +8049,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8131,7 +8096,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8145,10 +8110,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45474</v>
+        <v>46153</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8160,8 +8125,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8204,7 +8174,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8218,10 +8188,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46142</v>
+        <v>45607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8234,7 +8204,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8277,7 +8247,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8291,10 +8261,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46146</v>
+        <v>45966</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8306,13 +8276,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>12.1</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8355,7 +8320,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8369,10 +8334,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46148</v>
+        <v>45764</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8384,8 +8349,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8428,7 +8398,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8442,10 +8412,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45103</v>
+        <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8457,8 +8427,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8501,7 +8476,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8515,10 +8490,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46148</v>
+        <v>44852</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8531,7 +8506,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8574,7 +8549,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8588,10 +8563,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46149</v>
+        <v>44973</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8604,7 +8579,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8647,7 +8622,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8657,14 +8632,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45537</v>
+        <v>45320</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8677,7 +8652,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8720,7 +8695,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8734,10 +8709,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46153</v>
+        <v>45454</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8749,13 +8724,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8798,7 +8768,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8812,10 +8782,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46153</v>
+        <v>45454</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8825,11 +8795,6 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -8876,7 +8841,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8890,10 +8855,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44852</v>
+        <v>45989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8906,7 +8871,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8949,7 +8914,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8963,10 +8928,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45191</v>
+        <v>45964</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8978,13 +8943,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9027,7 +8987,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9037,14 +8997,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45089</v>
+        <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9057,7 +9017,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9100,7 +9060,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9110,14 +9070,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45937</v>
+        <v>45769</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9130,7 +9090,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9173,7 +9133,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9187,10 +9147,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45937</v>
+        <v>45408</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9202,8 +9162,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9246,7 +9211,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9256,14 +9221,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45974</v>
+        <v>46006</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9276,7 +9241,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9319,7 +9284,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9333,10 +9298,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44992</v>
+        <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9349,7 +9314,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9392,7 +9357,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9406,10 +9371,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45607</v>
+        <v>45056</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9422,7 +9387,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9465,7 +9430,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9479,10 +9444,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45588</v>
+        <v>45155</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9494,8 +9459,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9538,7 +9508,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9552,10 +9522,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45028</v>
+        <v>46014</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9568,7 +9538,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9611,7 +9581,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9625,10 +9595,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46176</v>
+        <v>46014</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9640,13 +9610,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>7.4</v>
+        <v>22.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9689,7 +9654,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9699,14 +9664,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45567</v>
+        <v>45056</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9719,7 +9684,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9762,7 +9727,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9776,10 +9741,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45063</v>
+        <v>45639</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9792,7 +9757,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9835,7 +9800,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9849,10 +9814,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46189</v>
+        <v>46020</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9864,13 +9829,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>13.7</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9913,7 +9873,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9927,10 +9887,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45205</v>
+        <v>45474</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9942,13 +9902,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9991,7 +9946,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10005,10 +9960,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46189</v>
+        <v>45588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10020,13 +9975,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10069,7 +10019,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10083,10 +10033,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46190</v>
+        <v>44973</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10100,11 +10050,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10147,7 +10097,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10161,10 +10111,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45121</v>
+        <v>45034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10176,8 +10126,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10220,7 +10175,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10234,10 +10189,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45966</v>
+        <v>46045</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10250,7 +10205,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10293,7 +10248,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10307,10 +10262,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44628</v>
+        <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10322,8 +10277,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10366,7 +10326,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10380,10 +10340,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45440</v>
+        <v>45155</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10395,8 +10355,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10439,7 +10404,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10449,14 +10414,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10470,11 +10435,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10517,7 +10482,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10531,10 +10496,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45196</v>
+        <v>45474</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10546,13 +10511,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10595,7 +10555,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10609,10 +10569,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46153</v>
+        <v>45613</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10624,13 +10584,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10673,7 +10628,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10687,10 +10642,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46246</v>
+        <v>46189</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10702,8 +10657,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.5</v>
+        <v>13.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10746,7 +10706,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10760,10 +10720,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45232</v>
+        <v>46093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10775,13 +10735,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10824,7 +10779,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10838,10 +10793,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46247</v>
+        <v>46093</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10853,13 +10808,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10902,7 +10852,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10916,10 +10866,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45639</v>
+        <v>46189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10931,8 +10881,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10975,7 +10930,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10989,10 +10944,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45408</v>
+        <v>46190</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11010,7 +10965,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11053,7 +11008,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11067,10 +11022,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45699</v>
+        <v>46099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11082,8 +11037,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11126,7 +11086,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11140,10 +11100,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45169</v>
+        <v>45408</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11161,7 +11121,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11204,7 +11164,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11218,10 +11178,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45989</v>
+        <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11233,8 +11193,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11277,7 +11242,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11291,10 +11256,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45155</v>
+        <v>45560</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11308,11 +11273,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11355,7 +11320,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11369,10 +11334,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45964</v>
+        <v>46105</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11385,7 +11350,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11428,7 +11393,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11442,10 +11407,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46258</v>
+        <v>46105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11457,13 +11422,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11506,7 +11466,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11520,10 +11480,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45679</v>
+        <v>46105</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11535,8 +11495,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11579,7 +11544,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11593,10 +11558,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45226</v>
+        <v>46108</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11614,7 +11579,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11657,7 +11622,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11671,10 +11636,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45730</v>
+        <v>46111</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11686,8 +11651,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11730,7 +11700,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11744,10 +11714,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45049</v>
+        <v>46114</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11759,8 +11729,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11803,7 +11778,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11817,10 +11792,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46265</v>
+        <v>45200</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11838,7 +11813,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11881,7 +11856,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11895,10 +11870,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46223</v>
+        <v>46113</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11910,8 +11885,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11954,7 +11934,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11968,10 +11948,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46265</v>
+        <v>45769</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11985,11 +11965,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12032,7 +12012,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12046,10 +12026,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46006</v>
+        <v>46119</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12061,8 +12041,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>3.2</v>
+        <v>6.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12105,7 +12090,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12119,10 +12104,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46268</v>
+        <v>45089</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12134,13 +12119,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>8.9</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12183,7 +12163,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12197,10 +12177,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46268</v>
+        <v>45588</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12212,13 +12192,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12261,7 +12236,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12275,10 +12250,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12290,8 +12265,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12334,7 +12314,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12348,10 +12328,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46008</v>
+        <v>46153</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12363,8 +12343,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12407,7 +12392,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12417,14 +12402,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45274</v>
+        <v>45063</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12437,7 +12422,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12480,7 +12465,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12494,10 +12479,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46014</v>
+        <v>45607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12510,7 +12495,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>22.8</v>
+        <v>0.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12553,7 +12538,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12567,10 +12552,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46014</v>
+        <v>45049</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12583,7 +12568,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12626,7 +12611,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12640,10 +12625,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46197</v>
+        <v>44523</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12655,13 +12640,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12704,7 +12684,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12718,10 +12698,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46197</v>
+        <v>45405</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12733,13 +12713,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12782,7 +12757,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12792,14 +12767,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46253</v>
+        <v>44480</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12812,7 +12787,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12855,7 +12830,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12869,10 +12844,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46020</v>
+        <v>46246</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12885,7 +12860,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12928,7 +12903,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12942,10 +12917,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45769</v>
+        <v>46247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12959,11 +12934,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13006,7 +12981,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13020,10 +12995,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45769</v>
+        <v>45233</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13037,11 +13012,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13084,7 +13059,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13098,10 +13073,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46266</v>
+        <v>45121</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13113,13 +13088,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13162,7 +13132,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13172,14 +13142,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46232</v>
+        <v>45028</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13191,13 +13161,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13240,7 +13205,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13254,10 +13219,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46232</v>
+        <v>45089</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13270,7 +13235,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13313,7 +13278,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13327,10 +13292,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45001</v>
+        <v>45567</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13343,7 +13308,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>22.4</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13386,7 +13351,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13400,10 +13365,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46233</v>
+        <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13421,7 +13386,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13464,7 +13429,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13478,10 +13443,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45607</v>
+        <v>44727</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13493,8 +13458,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13537,7 +13507,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13551,10 +13521,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45200</v>
+        <v>45607</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13566,13 +13536,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13615,7 +13580,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13625,14 +13590,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46238</v>
+        <v>44992</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13645,7 +13610,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13688,7 +13653,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13702,10 +13667,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45560</v>
+        <v>45169</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13719,11 +13684,11 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13766,7 +13731,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13780,10 +13745,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46045</v>
+        <v>46265</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13795,8 +13760,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13839,7 +13809,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13853,10 +13823,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45056</v>
+        <v>46265</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13868,8 +13838,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13912,7 +13887,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13926,10 +13901,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45233</v>
+        <v>45169</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13947,7 +13922,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13990,7 +13965,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14004,10 +13979,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45454</v>
+        <v>46223</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14020,7 +13995,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14063,7 +14038,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14077,10 +14052,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45454</v>
+        <v>46268</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14092,8 +14067,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14136,7 +14116,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14150,10 +14130,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44727</v>
+        <v>45440</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14165,13 +14145,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14214,7 +14189,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14228,10 +14203,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45588</v>
+        <v>46268</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14243,8 +14218,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14287,7 +14267,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14301,10 +14281,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45179</v>
+        <v>45191</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14318,11 +14298,11 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14365,7 +14345,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14375,14 +14355,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45607</v>
+        <v>45196</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14394,8 +14374,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14438,7 +14423,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14448,14 +14433,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45769</v>
+        <v>46197</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14467,8 +14452,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14511,7 +14501,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14525,10 +14515,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45316</v>
+        <v>46197</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14540,8 +14530,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14584,7 +14579,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14598,10 +14593,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45567</v>
+        <v>45390</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14614,7 +14609,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14657,7 +14652,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14671,10 +14666,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45632</v>
+        <v>46253</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14686,13 +14681,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14735,7 +14725,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14749,10 +14739,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44691</v>
+        <v>46266</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14766,11 +14756,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14813,7 +14803,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14827,10 +14817,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45729</v>
+        <v>46232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14843,7 +14833,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14886,7 +14876,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14896,14 +14886,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45586</v>
+        <v>46232</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14915,8 +14905,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14959,7 +14954,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14973,10 +14968,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45597</v>
+        <v>46233</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14988,8 +14983,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15032,7 +15032,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15042,14 +15042,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45034</v>
+        <v>46238</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15061,13 +15061,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15110,7 +15105,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15124,10 +15119,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44992</v>
+        <v>45792</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15139,8 +15134,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15183,7 +15183,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15197,10 +15197,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45191</v>
+        <v>45792</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15214,11 +15214,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15261,7 +15261,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15275,10 +15275,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45196</v>
+        <v>45576</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15292,11 +15292,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45390</v>
+        <v>45274</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15412,7 +15412,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15426,10 +15426,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45792</v>
+        <v>45825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15441,13 +15441,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15490,7 +15485,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15504,10 +15499,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45792</v>
+        <v>45827</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15525,7 +15520,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15568,7 +15563,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15582,10 +15577,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45274</v>
+        <v>45882</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15597,8 +15592,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>15</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15641,7 +15641,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45576</v>
+        <v>45882</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>9.300000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
         <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>46019</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>46105</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>45622</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45773</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45644</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>46139</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45142</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45762</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46196</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>44873</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>46268</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>46253</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>45882</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45737</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44860</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44873</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44600</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44852</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44838</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44620</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44480</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44831</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45196</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>45699</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44552</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>45155</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>45363</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45226</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45705</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45200</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>45730</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>45316</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>45274</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45179</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44691</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45001</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44628</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>45729</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>45405</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>45769</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45554</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44860</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>45598</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45232</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45679</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45631</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44992</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>46142</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>45597</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45937</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>46148</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46148</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45537</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>46149</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>46153</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>46153</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45966</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45764</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44852</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44973</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45320</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45454</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45454</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>45989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45964</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45769</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45408</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>46006</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45056</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45155</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>46014</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>46014</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45056</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45639</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>46020</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45474</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44973</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>46045</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45155</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45994</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45474</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45613</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>46189</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>46093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>46093</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>46189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>46190</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>46099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45408</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45560</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>46105</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>46105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>46105</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>46108</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>46111</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>46114</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45200</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>46113</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45769</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>46119</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>45089</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45588</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45632</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>46153</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45063</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45049</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44523</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45405</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44480</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>46246</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>46247</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45233</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45121</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45028</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45089</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45567</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44727</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45607</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44992</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45169</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>46265</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>46265</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45169</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>46223</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>46268</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45440</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>46268</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45191</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45196</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>46197</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>46197</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45390</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>46253</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46266</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>46232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>46232</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>46233</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>46238</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45792</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>45792</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45576</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45274</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45827</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45882</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45882</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE193"/>
+  <dimension ref="A1:AE194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>46019</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>46105</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 55711-2024</t>
+          <t>A 36009-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45622</v>
+        <v>46266</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1510,17 +1510,22 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1535,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1547,151 +1552,146 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 55711-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45622</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Persiljespindling
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 36009-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
         <v/>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45773</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45644</v>
+        <v>45882</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2268,24 +2268,29 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>15.5</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -2293,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2309,42 +2314,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46139</v>
+        <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2374,7 +2379,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2410,50 +2415,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2467,10 +2468,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45142</v>
+        <v>46139</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2482,22 +2483,17 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2512,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2528,42 +2524,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45762</v>
+        <v>45142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2594,35 +2594,35 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2631,42 +2631,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
         <v>46196</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44873</v>
+        <v>45762</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,14 +2812,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2846,49 +2851,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46268</v>
+        <v>44873</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,19 +2922,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2963,42 +2963,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,8 +3027,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3068,42 +3073,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3120,7 +3125,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3133,7 +3138,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3177,38 +3182,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3222,10 +3227,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45882</v>
+        <v>46253</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,19 +3242,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>15.5</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3267,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,59 +3283,59 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S 4857-2024</t>
+          <t>A 38927-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45608</v>
+        <v>46282</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>79.3</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3388,42 +3388,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/S 4857-2024 artfynd.xlsx", "S 4857-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/S 4857-2024 karta.png", "S 4857-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/S 4857-2024 georefererad karta.tif", "S 4857-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/S 4857-2024 FSC-klagomål.docx", "S 4857-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/S 4857-2024 FSC-klagomål mail.docx", "S 4857-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/S 4857-2024 tillsynsbegäran.docx", "S 4857-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/S 4857-2024 tillsynsbegäran mail.docx", "S 4857-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S 920-2025</t>
+          <t>S 4857-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45737</v>
+        <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3452,13 +3452,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>79.3</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3467,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3482,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3498,59 +3493,59 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/S 920-2025 artfynd.xlsx", "S 920-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/S 4857-2024 artfynd.xlsx", "S 4857-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/S 920-2025 karta.png", "S 920-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/S 4857-2024 karta.png", "S 4857-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/S 920-2025 georefererad karta.tif", "S 920-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/S 4857-2024 georefererad karta.tif", "S 4857-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/S 920-2025 FSC-klagomål.docx", "S 920-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/S 4857-2024 FSC-klagomål.docx", "S 4857-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/S 920-2025 FSC-klagomål mail.docx", "S 920-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/S 4857-2024 FSC-klagomål mail.docx", "S 4857-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/S 920-2025 tillsynsbegäran.docx", "S 920-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/S 4857-2024 tillsynsbegäran.docx", "S 4857-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/S 920-2025 tillsynsbegäran mail.docx", "S 920-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/S 4857-2024 tillsynsbegäran mail.docx", "S 4857-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51415-2022</t>
+          <t>S 920-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44869</v>
+        <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3564,14 +3559,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3598,20 +3593,52 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/S 920-2025 artfynd.xlsx", "S 920-2025")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/S 920-2025 karta.png", "S 920-2025")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/S 920-2025 georefererad karta.tif", "S 920-2025")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/S 920-2025 FSC-klagomål.docx", "S 920-2025")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/S 920-2025 FSC-klagomål mail.docx", "S 920-2025")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/S 920-2025 tillsynsbegäran.docx", "S 920-2025")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/S 920-2025 tillsynsbegäran mail.docx", "S 920-2025")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49143-2022</t>
+          <t>A 51415-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3625,10 +3652,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44860</v>
+        <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3642,11 +3669,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3689,7 +3716,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49163-2022</t>
+          <t>A 49143-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3706,7 +3733,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3724,7 +3751,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3767,7 +3794,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44016-2022</t>
+          <t>A 49163-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3781,10 +3808,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44838</v>
+        <v>44860</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3802,7 +3829,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3845,7 +3872,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 52076-2022</t>
+          <t>A 44016-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3855,14 +3882,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44873</v>
+        <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3874,8 +3901,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3918,7 +3950,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6353-2022</t>
+          <t>A 52076-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3928,14 +3960,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44600</v>
+        <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3948,7 +3980,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3991,7 +4023,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47607-2022</t>
+          <t>A 6353-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4005,10 +4037,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44852</v>
+        <v>44600</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4021,7 +4053,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4064,7 +4096,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 44015-2022</t>
+          <t>A 47607-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,10 +4110,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44838</v>
+        <v>44852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4093,13 +4125,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4142,7 +4169,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9875-2022</t>
+          <t>A 44015-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4156,10 +4183,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44620</v>
+        <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4171,8 +4198,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4215,7 +4247,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 46641-2022</t>
+          <t>A 9875-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4229,10 +4261,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44849</v>
+        <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4244,13 +4276,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4293,7 +4320,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56929-2021</t>
+          <t>A 46641-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4303,14 +4330,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44480</v>
+        <v>44849</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4322,8 +4349,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4366,7 +4398,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42504-2022</t>
+          <t>A 56929-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4376,14 +4408,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44831</v>
+        <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4395,13 +4427,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4444,7 +4471,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42505-2022</t>
+          <t>A 42504-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4461,7 +4488,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4479,7 +4506,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4522,7 +4549,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12233-2022</t>
+          <t>A 42505-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4536,10 +4563,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44635</v>
+        <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4551,8 +4578,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4595,7 +4627,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2312-2022</t>
+          <t>A 12233-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4605,14 +4637,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44578</v>
+        <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4668,7 +4700,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 67361-2021</t>
+          <t>A 2312-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4678,14 +4710,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44523</v>
+        <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4698,7 +4730,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4741,7 +4773,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 67361-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4755,10 +4787,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45196</v>
+        <v>44523</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4770,13 +4802,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4819,7 +4846,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4833,10 +4860,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45699</v>
+        <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4848,8 +4875,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4892,7 +4924,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4906,10 +4938,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45631</v>
+        <v>45699</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4922,7 +4954,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4965,7 +4997,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4979,10 +5011,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45607</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4995,7 +5027,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5038,7 +5070,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5052,10 +5084,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44552</v>
+        <v>45607</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5068,7 +5100,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5111,7 +5143,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5125,10 +5157,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45155</v>
+        <v>44552</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5140,13 +5172,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5189,7 +5216,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5203,10 +5230,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45363</v>
+        <v>45155</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5218,8 +5245,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5262,7 +5294,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5276,10 +5308,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45226</v>
+        <v>45363</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5291,13 +5323,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5357,7 +5384,7 @@
         <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5413,7 +5440,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5427,10 +5454,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45705</v>
+        <v>45226</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5442,8 +5469,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5486,7 +5518,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5500,10 +5532,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45200</v>
+        <v>45705</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5515,13 +5547,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5564,7 +5591,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5578,10 +5605,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45567</v>
+        <v>45200</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5593,8 +5620,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5637,7 +5669,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5651,10 +5683,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45730</v>
+        <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5667,7 +5699,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5710,7 +5742,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5724,10 +5756,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45316</v>
+        <v>45730</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5740,7 +5772,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5783,7 +5815,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5793,14 +5825,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45274</v>
+        <v>45316</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5813,7 +5845,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5856,7 +5888,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5866,14 +5898,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45179</v>
+        <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5885,13 +5917,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5934,7 +5961,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5948,10 +5975,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45586</v>
+        <v>45179</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5963,8 +5990,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6024,7 +6056,7 @@
         <v>44691</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6102,7 +6134,7 @@
         <v>45001</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6175,7 +6207,7 @@
         <v>44628</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6231,7 +6263,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6245,10 +6277,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45729</v>
+        <v>45882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6260,8 +6292,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6304,7 +6341,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6318,10 +6355,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45405</v>
+        <v>45882</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6333,8 +6370,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6377,7 +6419,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6391,10 +6433,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45769</v>
+        <v>45729</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6406,13 +6448,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6455,7 +6492,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6465,14 +6502,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45554</v>
+        <v>44480</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6485,7 +6522,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6528,7 +6565,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6542,10 +6579,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45169</v>
+        <v>45405</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6557,13 +6594,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6606,7 +6638,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6620,10 +6652,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44860</v>
+        <v>45769</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6635,8 +6667,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6679,7 +6716,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6693,10 +6730,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45598</v>
+        <v>45554</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6708,13 +6745,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6757,7 +6789,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6771,10 +6803,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45232</v>
+        <v>45169</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6792,7 +6824,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6835,7 +6867,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6849,10 +6881,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45679</v>
+        <v>45598</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6864,8 +6896,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6908,7 +6945,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6922,10 +6959,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45631</v>
+        <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6938,7 +6975,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6981,7 +7018,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6995,10 +7032,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44992</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7011,7 +7048,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7054,7 +7091,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7068,10 +7105,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45205</v>
+        <v>45232</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7089,7 +7126,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7132,7 +7169,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7146,10 +7183,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45918</v>
+        <v>45679</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7162,7 +7199,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7205,7 +7242,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7215,14 +7252,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45191</v>
+        <v>46142</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7234,13 +7271,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7283,7 +7315,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7293,14 +7325,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7312,8 +7344,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>12.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7356,7 +7393,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7370,10 +7407,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45937</v>
+        <v>46148</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7386,7 +7423,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7429,7 +7466,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7443,10 +7480,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46146</v>
+        <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7458,13 +7495,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>12.1</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7507,7 +7539,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7521,10 +7553,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45597</v>
+        <v>45631</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7537,7 +7569,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7580,7 +7612,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7594,10 +7626,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45937</v>
+        <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7610,7 +7642,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7653,7 +7685,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7667,10 +7699,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7683,7 +7715,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7726,7 +7758,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7740,10 +7772,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46148</v>
+        <v>45937</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7756,7 +7788,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7799,7 +7831,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7813,10 +7845,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45537</v>
+        <v>46153</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7828,8 +7860,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7872,7 +7909,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7886,10 +7923,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7901,8 +7938,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7945,7 +7987,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7959,10 +8001,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45103</v>
+        <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7975,7 +8017,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8018,7 +8060,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8032,10 +8074,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46153</v>
+        <v>45205</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8049,11 +8091,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8096,7 +8138,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8110,10 +8152,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46153</v>
+        <v>45191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8127,11 +8169,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8174,7 +8216,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8188,10 +8230,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45607</v>
+        <v>45974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8204,7 +8246,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8264,7 +8306,7 @@
         <v>45966</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8320,7 +8362,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8334,10 +8376,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45764</v>
+        <v>45597</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8349,13 +8391,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8415,7 +8452,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8476,7 +8513,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8490,10 +8527,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44852</v>
+        <v>45537</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8506,7 +8543,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8549,7 +8586,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8563,10 +8600,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44973</v>
+        <v>45103</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8579,7 +8616,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8622,7 +8659,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8632,14 +8669,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45320</v>
+        <v>45989</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8652,7 +8689,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8695,7 +8732,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8709,10 +8746,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45454</v>
+        <v>45964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8725,7 +8762,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8768,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8778,14 +8815,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45454</v>
+        <v>45607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8798,7 +8835,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8841,7 +8878,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8855,10 +8892,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45989</v>
+        <v>46176</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8870,8 +8907,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8914,7 +8956,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8928,10 +8970,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45964</v>
+        <v>46006</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8944,7 +8986,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8987,7 +9029,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8997,14 +9039,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45974</v>
+        <v>46008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9017,7 +9059,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9060,7 +9102,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9070,14 +9112,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45769</v>
+        <v>45764</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9089,8 +9131,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9133,7 +9180,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9147,10 +9194,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45408</v>
+        <v>46014</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9162,13 +9209,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>8.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9211,7 +9253,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9225,10 +9267,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9241,7 +9283,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.2</v>
+        <v>22.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9284,7 +9326,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9298,10 +9340,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46008</v>
+        <v>46020</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9314,7 +9356,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9357,7 +9399,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9371,10 +9413,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45056</v>
+        <v>44852</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9387,7 +9429,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9430,7 +9472,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9444,10 +9486,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45155</v>
+        <v>44973</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9459,13 +9501,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9508,7 +9545,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9518,14 +9555,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46014</v>
+        <v>45320</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9538,7 +9575,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9581,7 +9618,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9595,10 +9632,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46014</v>
+        <v>45454</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9611,7 +9648,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>22.8</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9654,7 +9691,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9664,14 +9701,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45056</v>
+        <v>45454</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9684,7 +9721,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9727,7 +9764,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9741,10 +9778,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45639</v>
+        <v>46189</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9756,8 +9793,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>13.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9800,7 +9842,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9814,10 +9856,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46020</v>
+        <v>46045</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9830,7 +9872,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9873,7 +9915,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9887,10 +9929,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45474</v>
+        <v>46189</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9902,8 +9944,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9946,7 +9993,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9960,10 +10007,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45588</v>
+        <v>46190</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9975,8 +10022,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10019,7 +10071,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10029,14 +10081,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44973</v>
+        <v>45769</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10048,13 +10100,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10097,7 +10144,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10111,10 +10158,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45034</v>
+        <v>45408</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10128,11 +10175,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10175,7 +10222,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10185,14 +10232,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46045</v>
+        <v>45994</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10204,8 +10251,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10248,7 +10300,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10262,10 +10314,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46176</v>
+        <v>45056</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10277,13 +10329,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10326,7 +10373,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10343,7 +10390,7 @@
         <v>45155</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10357,11 +10404,11 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10404,7 +10451,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10418,10 +10465,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45994</v>
+        <v>45056</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10433,13 +10480,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10482,7 +10524,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10496,10 +10538,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45474</v>
+        <v>45639</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10512,7 +10554,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10555,7 +10597,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10569,10 +10611,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45613</v>
+        <v>45474</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10585,7 +10627,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10628,7 +10670,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10642,10 +10684,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46189</v>
+        <v>45588</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10657,13 +10699,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>13.7</v>
+        <v>2.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10706,7 +10743,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10720,10 +10757,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46093</v>
+        <v>44973</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10735,8 +10772,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10779,7 +10821,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10796,7 +10838,7 @@
         <v>46093</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10809,7 +10851,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10852,7 +10894,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10866,10 +10908,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46189</v>
+        <v>46093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10881,13 +10923,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10930,7 +10967,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10944,10 +10981,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46190</v>
+        <v>46153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10961,11 +10998,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11025,7 +11062,7 @@
         <v>46099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11086,7 +11123,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11100,10 +11137,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45408</v>
+        <v>46105</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11115,13 +11152,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11164,7 +11196,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11178,10 +11210,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45169</v>
+        <v>46105</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11193,13 +11225,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11242,7 +11269,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11256,10 +11283,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45560</v>
+        <v>46105</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11273,11 +11300,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11320,7 +11347,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11334,10 +11361,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46105</v>
+        <v>45034</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11349,8 +11376,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11393,7 +11425,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11407,10 +11439,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11422,8 +11454,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11466,7 +11503,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11480,10 +11517,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46105</v>
+        <v>46246</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11495,13 +11532,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11544,7 +11576,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11558,10 +11590,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11579,7 +11611,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11622,7 +11654,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11636,10 +11668,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46111</v>
+        <v>46247</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11689,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11717,7 +11749,7 @@
         <v>46114</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11778,7 +11810,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11792,10 +11824,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45200</v>
+        <v>46113</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11813,7 +11845,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11856,7 +11888,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11870,10 +11902,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11891,7 +11923,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11934,7 +11966,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11948,10 +11980,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45769</v>
+        <v>45155</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11969,7 +12001,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12012,7 +12044,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12026,10 +12058,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46119</v>
+        <v>45474</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12041,13 +12073,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12090,7 +12117,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12104,10 +12131,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45089</v>
+        <v>45613</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12120,7 +12147,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12163,7 +12190,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12177,10 +12204,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45588</v>
+        <v>45408</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12192,8 +12219,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12236,7 +12268,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12250,10 +12282,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45632</v>
+        <v>46258</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12267,11 +12299,11 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12314,7 +12346,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12328,10 +12360,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46153</v>
+        <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12345,11 +12377,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12392,7 +12424,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12406,10 +12438,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45063</v>
+        <v>45560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12421,8 +12453,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12465,7 +12502,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12479,10 +12516,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45607</v>
+        <v>45200</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12494,8 +12531,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.1</v>
+        <v>5.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12538,7 +12580,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12552,10 +12594,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45049</v>
+        <v>45769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12567,8 +12609,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12611,7 +12658,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12625,10 +12672,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44523</v>
+        <v>45089</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12641,7 +12688,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12684,7 +12731,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12698,10 +12745,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45405</v>
+        <v>46265</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12713,8 +12760,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12757,7 +12809,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12767,14 +12819,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44480</v>
+        <v>46265</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12786,8 +12838,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12830,7 +12887,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12844,10 +12901,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46246</v>
+        <v>45588</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12860,7 +12917,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12903,7 +12960,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12917,10 +12974,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46247</v>
+        <v>46223</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12932,13 +12989,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12981,7 +13033,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12995,10 +13047,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45233</v>
+        <v>45632</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13012,11 +13064,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13059,7 +13111,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13073,10 +13125,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45121</v>
+        <v>45063</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13089,7 +13141,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13132,7 +13184,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13146,10 +13198,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45028</v>
+        <v>46268</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13161,8 +13213,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13205,7 +13262,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13219,10 +13276,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45089</v>
+        <v>45607</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13235,7 +13292,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13278,7 +13335,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13292,10 +13349,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45567</v>
+        <v>45049</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13308,7 +13365,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13351,7 +13408,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13365,10 +13422,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46258</v>
+        <v>46268</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13386,7 +13443,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>8.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13429,7 +13486,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13443,10 +13500,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44727</v>
+        <v>44523</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13458,13 +13515,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13507,7 +13559,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13521,10 +13573,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45607</v>
+        <v>46197</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13536,8 +13588,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13580,7 +13637,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13594,10 +13651,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44992</v>
+        <v>46197</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13609,8 +13666,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13653,7 +13715,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13667,10 +13729,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45169</v>
+        <v>45405</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13682,13 +13744,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13731,7 +13788,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13745,10 +13802,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46265</v>
+        <v>46253</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13760,13 +13817,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13809,7 +13861,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13823,10 +13875,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13844,7 +13896,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13887,7 +13939,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13901,10 +13953,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45169</v>
+        <v>46232</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13916,13 +13968,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13965,7 +14012,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13979,10 +14026,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46223</v>
+        <v>45233</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13994,8 +14041,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14038,7 +14090,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14048,14 +14100,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46268</v>
+        <v>46232</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14069,11 +14121,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14116,7 +14168,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14130,10 +14182,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45440</v>
+        <v>46233</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14145,8 +14197,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14189,7 +14246,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14203,10 +14260,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46268</v>
+        <v>45121</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14218,13 +14275,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14267,7 +14319,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14281,10 +14333,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45191</v>
+        <v>45028</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14296,13 +14348,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14345,7 +14392,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14355,14 +14402,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45196</v>
+        <v>46238</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14374,13 +14421,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14423,7 +14465,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14437,10 +14479,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46197</v>
+        <v>45089</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14452,13 +14494,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14501,7 +14538,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14515,10 +14552,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46197</v>
+        <v>45567</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14530,13 +14567,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14579,7 +14611,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14593,10 +14625,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45390</v>
+        <v>44727</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14608,8 +14640,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14652,7 +14689,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14666,10 +14703,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46253</v>
+        <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14682,7 +14719,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14725,7 +14762,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14739,10 +14776,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46266</v>
+        <v>45586</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14754,13 +14791,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14803,7 +14835,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14817,10 +14849,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46232</v>
+        <v>44992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14833,7 +14865,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14876,7 +14908,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14886,14 +14918,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46232</v>
+        <v>45169</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14907,11 +14939,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14954,7 +14986,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14968,10 +15000,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46233</v>
+        <v>45169</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14989,7 +15021,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15032,7 +15064,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15042,14 +15074,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46238</v>
+        <v>45440</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15062,7 +15094,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15105,7 +15137,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15119,10 +15151,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45792</v>
+        <v>45191</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15136,11 +15168,11 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15183,7 +15215,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15197,10 +15229,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45792</v>
+        <v>45196</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15214,11 +15246,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15261,7 +15293,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15275,10 +15307,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45576</v>
+        <v>45390</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15290,13 +15322,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>9.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15339,7 +15366,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15353,10 +15380,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45274</v>
+        <v>45792</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15368,8 +15395,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15412,7 +15444,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15426,10 +15458,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45825</v>
+        <v>45792</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15441,8 +15473,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15485,7 +15522,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15499,10 +15536,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45827</v>
+        <v>45576</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15520,7 +15557,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15563,7 +15600,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15577,10 +15614,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45882</v>
+        <v>45274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15592,13 +15629,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>15</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15641,7 +15673,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15655,10 +15687,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45882</v>
+        <v>45825</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15670,13 +15702,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15719,24 +15746,24 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>S 409-2022</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44585</v>
+        <v>45827</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15750,11 +15777,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>10.9</v>
+        <v>4.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15797,153 +15824,231 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
+          <t>S 409-2022</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>44585</v>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193" ht="15" customHeight="1">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>S 606-2026</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D192" s="1" t="n">
+      <c r="D193" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="E192" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
+      <c r="E193" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I192" t="n">
+      <c r="I193" t="n">
         <v>26.4</v>
       </c>
-      <c r="J192" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0</v>
-      </c>
-      <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="n">
-        <v>0</v>
-      </c>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="n">
-        <v>0</v>
-      </c>
-      <c r="T192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="n">
-        <v>0</v>
-      </c>
-      <c r="V192" s="2" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>S 2097-2026</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D193" s="1" t="n">
+      <c r="D194" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="E193" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I193" t="n">
+      <c r="E194" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
         <v>0.8</v>
       </c>
-      <c r="J193" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" t="n">
-        <v>0</v>
-      </c>
-      <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="n">
-        <v>0</v>
-      </c>
-      <c r="V193" s="2" t="inlineStr"/>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18128-2024</t>
+          <t>A 33377-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45420</v>
+        <v>45128</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1074,11 +1074,16 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1087,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1099,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1115,694 +1120,689 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Gul taggsvamp
+Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 33377-2023 artfynd.xlsx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 33377-2023 karta.png", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 33377-2023 georefererad karta.tif", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 33377-2023 FSC-klagomål.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 33377-2023 FSC-klagomål mail.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 33377-2023 tillsynsbegäran.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 33377-2023 tillsynsbegäran mail.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 18128-2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45420</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Gulsparv
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18128-2024 artfynd.xlsx", "A 18128-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18128-2024 karta.png", "A 18128-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18128-2024 georefererad karta.tif", "A 18128-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18128-2024 FSC-klagomål.docx", "A 18128-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18128-2024 FSC-klagomål mail.docx", "A 18128-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18128-2024 tillsynsbegäran.docx", "A 18128-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18128-2024 tillsynsbegäran mail.docx", "A 18128-2024")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 18128-2024 prioriterade fågelarter.docx", "A 18128-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 63777-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46019</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 55711-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45622</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Persiljespindling
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 36009-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15262-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Brunklöver
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.4</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T11" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U11" t="n">
         <v>8</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 63777-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>3.4</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T12" t="n">
         <v>8</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U12" t="n">
         <v>8</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 15262-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 36009-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 55711-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45622</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Persiljespindling
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 33377-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45128</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Gul taggsvamp
-Dofttaggsvamp</t>
-        </is>
-      </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 33377-2023 artfynd.xlsx", "A 33377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 33377-2023 karta.png", "A 33377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 33377-2023 georefererad karta.tif", "A 33377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 33377-2023 FSC-klagomål.docx", "A 33377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 33377-2023 FSC-klagomål mail.docx", "A 33377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 33377-2023 tillsynsbegäran.docx", "A 33377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 33377-2023 tillsynsbegäran mail.docx", "A 33377-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45773</v>
+        <v>45762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2087,49 +2087,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45744</v>
+        <v>45773</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2200,46 +2200,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45882</v>
+        <v>44873</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2268,16 +2268,11 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>15.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2298,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2314,42 +2309,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2363,10 +2358,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45644</v>
+        <v>45142</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2378,18 +2373,23 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2415,46 +2415,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46139</v>
+        <v>45744</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2483,8 +2483,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2520,50 +2525,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 38927-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,10 +2578,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45142</v>
+        <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2592,22 +2593,17 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2622,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2634,46 +2630,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28307-2026</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2683,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46196</v>
+        <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2704,38 +2700,38 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>15.5</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2744,46 +2740,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2793,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45762</v>
+        <v>46139</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,19 +2808,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2851,49 +2842,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44873</v>
+        <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2923,7 +2918,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2967,38 +2962,38 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 28307-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46268</v>
+        <v>46196</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3033,7 +3028,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3069,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3077,38 +3072,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,10 +3117,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3137,8 +3132,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3178,42 +3178,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3230,7 +3230,7 @@
         <v>46253</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3287,38 +3287,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38927-2026</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -3388,35 +3388,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
         <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44860</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44600</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>44849</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2312-2022</t>
+          <t>A 67361-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44578</v>
+        <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 67361-2021</t>
+          <t>A 2312-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4783,14 +4783,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44523</v>
+        <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45196</v>
+        <v>45169</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4877,11 +4877,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45699</v>
+        <v>45390</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>45705</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5070,7 +5070,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45607</v>
+        <v>44552</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44552</v>
+        <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45155</v>
+        <v>45405</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5245,13 +5245,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5294,7 +5289,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5308,10 +5303,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45363</v>
+        <v>45155</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5323,8 +5318,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5367,7 +5367,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5377,14 +5377,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45154</v>
+        <v>44860</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>6.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5440,7 +5440,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45226</v>
+        <v>45200</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45705</v>
+        <v>45792</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5547,8 +5547,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5591,7 +5596,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5605,10 +5610,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45200</v>
+        <v>45792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5622,11 +5627,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5669,7 +5674,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5683,10 +5688,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45567</v>
+        <v>45764</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5698,8 +5703,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5742,7 +5752,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5756,10 +5766,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45730</v>
+        <v>45474</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5772,7 +5782,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5815,7 +5825,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5829,10 +5839,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45316</v>
+        <v>45474</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5845,7 +5855,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5888,7 +5898,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5898,14 +5908,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
         <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5918,7 +5928,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5961,7 +5971,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5975,10 +5985,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45179</v>
+        <v>45103</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5990,13 +6000,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6039,7 +6044,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6053,10 +6058,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44691</v>
+        <v>45537</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6068,13 +6073,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6117,7 +6117,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45001</v>
+        <v>45576</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6146,8 +6146,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>22.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6190,7 +6195,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6204,10 +6209,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44628</v>
+        <v>44852</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6220,7 +6225,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6263,7 +6268,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6277,10 +6282,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45882</v>
+        <v>45191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,11 +6299,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>15</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6341,7 +6346,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6351,14 +6356,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45882</v>
+        <v>45320</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6370,13 +6375,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45729</v>
+        <v>45089</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6502,14 +6502,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44480</v>
+        <v>45154</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45405</v>
+        <v>45169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6594,8 +6594,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6638,7 +6643,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6652,10 +6657,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45769</v>
+        <v>44992</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6667,13 +6672,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45554</v>
+        <v>44973</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45169</v>
+        <v>45607</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6818,13 +6818,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6867,7 +6862,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6881,10 +6876,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45598</v>
+        <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6896,13 +6891,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6945,7 +6935,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6959,10 +6949,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44860</v>
+        <v>45089</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6975,7 +6965,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7018,7 +7008,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7032,10 +7022,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>45588</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7091,7 +7081,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45232</v>
+        <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7120,13 +7110,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7169,7 +7154,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7179,14 +7164,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45679</v>
+        <v>45056</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7199,7 +7184,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7242,7 +7227,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7252,14 +7237,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46142</v>
+        <v>45567</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7272,7 +7257,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7315,7 +7300,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7329,10 +7314,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46146</v>
+        <v>45063</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7344,13 +7329,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>12.1</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7393,7 +7373,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7407,10 +7387,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46148</v>
+        <v>45408</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7422,8 +7402,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7483,7 +7468,7 @@
         <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7539,7 +7524,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7553,10 +7538,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45631</v>
+        <v>45937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7569,7 +7554,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7612,7 +7597,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7626,10 +7611,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46148</v>
+        <v>45205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7641,8 +7626,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7685,7 +7675,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7699,10 +7689,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46149</v>
+        <v>45405</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7715,7 +7705,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>7.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7758,7 +7748,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7772,10 +7762,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45937</v>
+        <v>45155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7787,8 +7777,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7831,7 +7826,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7845,10 +7840,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46153</v>
+        <v>44973</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7862,11 +7857,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7909,7 +7904,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7923,10 +7918,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46153</v>
+        <v>45121</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7938,13 +7933,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7987,7 +7977,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8001,10 +7991,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44992</v>
+        <v>44628</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8017,7 +8007,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8060,7 +8050,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8074,10 +8064,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45205</v>
+        <v>45440</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8089,13 +8079,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8138,7 +8123,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8152,10 +8137,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45191</v>
+        <v>45196</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8158,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8216,7 +8201,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8226,14 +8211,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45974</v>
+        <v>45966</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8231,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8289,7 +8274,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8303,10 +8288,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45966</v>
+        <v>45613</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8304,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8362,7 +8347,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8376,10 +8361,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45597</v>
+        <v>45607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8377,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8435,7 +8420,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8449,10 +8434,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45978</v>
+        <v>45363</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8464,13 +8449,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8513,7 +8493,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8527,10 +8507,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45537</v>
+        <v>45232</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8542,8 +8522,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8586,7 +8571,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8600,10 +8585,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45103</v>
+        <v>45639</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8601,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8659,7 +8644,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8673,10 +8658,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8688,8 +8673,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8732,7 +8722,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8746,10 +8736,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45964</v>
+        <v>45408</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8761,8 +8751,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8800,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8815,14 +8810,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45607</v>
+        <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8835,7 +8830,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8878,7 +8873,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8892,10 +8887,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46176</v>
+        <v>45989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8907,13 +8902,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8956,7 +8946,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8970,10 +8960,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46006</v>
+        <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8986,7 +8976,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9029,7 +9019,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9043,10 +9033,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46008</v>
+        <v>45169</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9058,8 +9048,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9102,7 +9097,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9116,10 +9111,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45764</v>
+        <v>45827</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9133,11 +9128,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9180,7 +9175,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9194,10 +9189,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46014</v>
+        <v>45964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9210,7 +9205,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9253,7 +9248,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9267,10 +9262,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46014</v>
+        <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9283,7 +9278,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>22.8</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9326,7 +9321,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9340,10 +9335,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46020</v>
+        <v>45155</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9355,8 +9350,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44852</v>
+        <v>45679</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9472,7 +9472,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44973</v>
+        <v>46006</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9555,14 +9555,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45320</v>
+        <v>45226</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9572,6 +9572,11 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -9618,7 +9623,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9632,10 +9637,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45454</v>
+        <v>45730</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9648,7 +9653,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9691,7 +9696,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9705,10 +9710,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45454</v>
+        <v>46008</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9721,7 +9726,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9764,7 +9769,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9778,10 +9783,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46189</v>
+        <v>45049</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9793,13 +9798,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>13.7</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9842,7 +9842,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46045</v>
+        <v>46014</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>22.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9915,7 +9915,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46189</v>
+        <v>46014</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9944,13 +9944,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9993,7 +9988,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10007,10 +10002,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46190</v>
+        <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10020,11 +10015,6 @@
       <c r="G115" t="inlineStr">
         <is>
           <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -10071,7 +10061,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10081,14 +10071,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45769</v>
+        <v>46020</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10101,7 +10091,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10144,7 +10134,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10154,14 +10144,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45408</v>
+        <v>46238</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10173,13 +10163,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10222,7 +10207,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10232,14 +10217,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45994</v>
+        <v>45631</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10251,13 +10236,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10300,7 +10280,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10310,14 +10290,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45056</v>
+        <v>45274</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10373,7 +10353,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10383,14 +10363,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45155</v>
+        <v>45994</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10404,11 +10384,11 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10451,7 +10431,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10461,14 +10441,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45056</v>
+        <v>45769</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10480,8 +10460,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10524,7 +10509,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10538,10 +10523,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45639</v>
+        <v>45769</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10553,8 +10538,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10597,7 +10587,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10611,10 +10601,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45474</v>
+        <v>46246</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10627,7 +10617,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10670,7 +10660,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10684,10 +10674,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45588</v>
+        <v>45001</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10700,7 +10690,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.9</v>
+        <v>22.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10743,7 +10733,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10757,10 +10747,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44973</v>
+        <v>45586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10772,13 +10762,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10821,7 +10806,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10835,10 +10820,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46093</v>
+        <v>46266</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10850,8 +10835,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10894,7 +10884,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10908,10 +10898,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46093</v>
+        <v>45607</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10924,7 +10914,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10967,7 +10957,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10981,10 +10971,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46153</v>
+        <v>45200</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10998,11 +10988,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11045,7 +11035,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11059,10 +11049,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46099</v>
+        <v>46093</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11074,13 +11064,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11123,7 +11108,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11137,10 +11122,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46105</v>
+        <v>46093</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11153,7 +11138,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11196,7 +11181,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11210,10 +11195,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46105</v>
+        <v>46099</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11225,8 +11210,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11269,7 +11259,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11286,7 +11276,7 @@
         <v>46105</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11298,13 +11288,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11347,7 +11332,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11361,10 +11346,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45034</v>
+        <v>46105</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11376,13 +11361,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11425,7 +11405,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11439,10 +11419,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46108</v>
+        <v>46105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11460,7 +11440,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11503,7 +11483,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11517,10 +11497,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46246</v>
+        <v>45560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11532,8 +11512,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11576,7 +11561,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11590,10 +11575,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11611,7 +11596,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11654,7 +11639,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11668,10 +11653,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46247</v>
+        <v>46111</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11689,7 +11674,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11732,7 +11717,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11746,10 +11731,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11767,7 +11752,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11810,7 +11795,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11824,10 +11809,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11845,7 +11830,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11905,7 +11890,7 @@
         <v>46119</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11966,7 +11951,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11980,10 +11965,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45155</v>
+        <v>45056</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11995,13 +11980,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12044,7 +12024,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12058,10 +12038,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45474</v>
+        <v>45233</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12073,8 +12053,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12117,7 +12102,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12131,10 +12116,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45613</v>
+        <v>45454</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12147,7 +12132,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12190,7 +12175,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12204,10 +12189,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45408</v>
+        <v>45454</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12219,13 +12204,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12268,7 +12248,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12282,10 +12262,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46258</v>
+        <v>44727</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12299,11 +12279,11 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12346,7 +12326,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12360,10 +12340,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45169</v>
+        <v>45882</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12377,11 +12357,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12424,7 +12404,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12438,10 +12418,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45560</v>
+        <v>45882</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12455,11 +12435,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12502,7 +12482,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12516,10 +12496,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45200</v>
+        <v>45588</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12531,13 +12511,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12580,7 +12555,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12594,10 +12569,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45769</v>
+        <v>45179</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12611,11 +12586,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12658,7 +12633,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12668,14 +12643,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45089</v>
+        <v>45607</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12688,7 +12663,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12731,7 +12706,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12741,14 +12716,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46265</v>
+        <v>44480</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12760,13 +12735,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12809,7 +12779,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12823,10 +12793,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46265</v>
+        <v>45554</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12838,13 +12808,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12887,7 +12852,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12897,14 +12862,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45588</v>
+        <v>45769</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12917,7 +12882,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12960,7 +12925,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12974,10 +12939,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46223</v>
+        <v>45169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12989,8 +12954,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>9.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13033,7 +13003,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13047,10 +13017,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45632</v>
+        <v>45598</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13064,11 +13034,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13111,7 +13081,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13125,10 +13095,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45063</v>
+        <v>45316</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13141,7 +13111,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13184,7 +13154,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13198,10 +13168,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46268</v>
+        <v>45567</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13213,13 +13183,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13262,7 +13227,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13276,10 +13241,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45607</v>
+        <v>45632</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13291,8 +13256,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13335,7 +13305,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13349,10 +13319,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45049</v>
+        <v>44691</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13364,8 +13334,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13408,7 +13383,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13422,10 +13397,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46268</v>
+        <v>45729</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13437,13 +13412,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13486,7 +13456,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13500,10 +13470,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44523</v>
+        <v>45597</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13516,7 +13486,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13559,7 +13529,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13569,14 +13539,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46197</v>
+        <v>46142</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13588,13 +13558,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13637,7 +13602,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13651,10 +13616,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46197</v>
+        <v>45034</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13668,11 +13633,11 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13715,7 +13680,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13729,10 +13694,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45405</v>
+        <v>44992</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13745,7 +13710,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13788,7 +13753,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13802,10 +13767,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46253</v>
+        <v>46146</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13817,8 +13782,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>12.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13861,7 +13831,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13875,10 +13845,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46266</v>
+        <v>46148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13890,13 +13860,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13939,7 +13904,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13953,10 +13918,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46232</v>
+        <v>46148</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13969,7 +13934,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14012,7 +13977,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14026,10 +13991,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45233</v>
+        <v>46149</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14041,13 +14006,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14090,7 +14050,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14100,14 +14060,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46232</v>
+        <v>46153</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14125,7 +14085,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14168,7 +14128,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14182,10 +14142,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46233</v>
+        <v>45191</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14199,11 +14159,11 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14246,7 +14206,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14260,10 +14220,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45121</v>
+        <v>45196</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14275,8 +14235,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14319,7 +14284,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14333,10 +14298,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45028</v>
+        <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14348,8 +14313,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14392,7 +14362,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14402,14 +14372,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46238</v>
+        <v>45974</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14422,7 +14392,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14465,7 +14435,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14479,10 +14449,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45089</v>
+        <v>46176</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14494,8 +14464,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14538,7 +14513,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14552,10 +14527,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45567</v>
+        <v>46189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14567,8 +14542,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>13.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14611,7 +14591,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14625,10 +14605,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44727</v>
+        <v>46189</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14642,11 +14622,11 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14689,7 +14669,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14703,10 +14683,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45607</v>
+        <v>46190</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14718,8 +14698,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14762,7 +14747,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14776,10 +14761,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45586</v>
+        <v>46153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14791,8 +14776,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14835,7 +14825,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14849,10 +14839,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44992</v>
+        <v>46247</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14864,8 +14854,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14908,7 +14903,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14922,10 +14917,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45169</v>
+        <v>46258</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14943,7 +14938,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14986,7 +14981,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15000,10 +14995,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45169</v>
+        <v>46265</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15021,7 +15016,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15064,7 +15059,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15078,10 +15073,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45440</v>
+        <v>46223</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15094,7 +15089,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15137,7 +15132,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15151,10 +15146,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45191</v>
+        <v>46265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15168,11 +15163,11 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15215,7 +15210,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15229,10 +15224,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45196</v>
+        <v>46268</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15246,11 +15241,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15293,7 +15288,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15307,10 +15302,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45390</v>
+        <v>46268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15322,8 +15317,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15366,7 +15366,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15380,10 +15380,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45792</v>
+        <v>46197</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15397,11 +15397,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15444,7 +15444,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15458,10 +15458,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45792</v>
+        <v>46197</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15475,11 +15475,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15522,7 +15522,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15536,10 +15536,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45576</v>
+        <v>46253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15551,13 +15551,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15600,7 +15595,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15610,14 +15605,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45274</v>
+        <v>46232</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15629,8 +15624,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15673,7 +15673,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15687,10 +15687,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45825</v>
+        <v>46232</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15746,7 +15746,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15760,10 +15760,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45827</v>
+        <v>46233</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15777,11 +15777,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>44585</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>46085</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 33377-2023</t>
+          <t>A 18128-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45128</v>
+        <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1074,16 +1074,11 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1092,22 +1087,22 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1120,689 +1115,694 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Gulsparv
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18128-2024 artfynd.xlsx", "A 18128-2024")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18128-2024 karta.png", "A 18128-2024")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18128-2024 georefererad karta.tif", "A 18128-2024")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18128-2024 FSC-klagomål.docx", "A 18128-2024")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18128-2024 FSC-klagomål mail.docx", "A 18128-2024")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18128-2024 tillsynsbegäran.docx", "A 18128-2024")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18128-2024 tillsynsbegäran mail.docx", "A 18128-2024")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 18128-2024 prioriterade fågelarter.docx", "A 18128-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 63777-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 15262-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Brunklöver
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55711-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45622</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Persiljespindling
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 33377-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45128</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Gul taggsvamp
 Dofttaggsvamp</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 33377-2023 artfynd.xlsx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 33377-2023 karta.png", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 33377-2023 georefererad karta.tif", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 33377-2023 FSC-klagomål.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 33377-2023 FSC-klagomål mail.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 33377-2023 tillsynsbegäran.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 33377-2023 tillsynsbegäran mail.docx", "A 33377-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 18128-2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45420</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J7" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 36009-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18128-2024 artfynd.xlsx", "A 18128-2024")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18128-2024 karta.png", "A 18128-2024")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18128-2024 georefererad karta.tif", "A 18128-2024")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18128-2024 FSC-klagomål.docx", "A 18128-2024")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18128-2024 FSC-klagomål mail.docx", "A 18128-2024")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18128-2024 tillsynsbegäran.docx", "A 18128-2024")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18128-2024 tillsynsbegäran mail.docx", "A 18128-2024")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 18128-2024 prioriterade fågelarter.docx", "A 18128-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 55711-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45622</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Persiljespindling
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 36009-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Gullviva</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15262-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 63777-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46019</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45762</v>
+        <v>45773</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2087,49 +2087,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45773</v>
+        <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2200,46 +2200,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44873</v>
+        <v>45882</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2268,24 +2268,29 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>15.5</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -2293,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2309,42 +2314,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45142</v>
+        <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2373,22 +2378,17 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2415,46 +2415,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45744</v>
+        <v>46139</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2483,13 +2483,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2525,46 +2520,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38927-2026</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2578,10 +2577,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46282</v>
+        <v>45142</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2593,18 +2592,23 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2618,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2630,46 +2634,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2683,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45882</v>
+        <v>45762</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,17 +2704,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>15.5</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2719,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2728,58 +2732,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 28307-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2793,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46139</v>
+        <v>46196</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2808,14 +2812,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2849,46 +2858,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45644</v>
+        <v>44873</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2918,7 +2923,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2962,38 +2967,38 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28307-2026</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46196</v>
+        <v>46268</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3028,7 +3033,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3064,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3072,38 +3077,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3117,10 +3122,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46268</v>
+        <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,13 +3137,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3178,42 +3178,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3230,7 +3230,7 @@
         <v>46253</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3287,38 +3287,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 38927-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -3388,35 +3388,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
         <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44860</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44600</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>44849</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45169</v>
+        <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4877,11 +4877,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45390</v>
+        <v>45699</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45705</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5070,7 +5070,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5084,10 +5084,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44552</v>
+        <v>45607</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44523</v>
+        <v>44552</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45405</v>
+        <v>45155</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5245,8 +5245,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5289,7 +5294,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5303,10 +5308,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45155</v>
+        <v>45363</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5318,13 +5323,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5367,7 +5367,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5377,14 +5377,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44860</v>
+        <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.8</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5440,7 +5440,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45200</v>
+        <v>45226</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45792</v>
+        <v>45705</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5547,13 +5547,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5596,7 +5591,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5610,10 +5605,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45792</v>
+        <v>45200</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5627,11 +5622,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5674,7 +5669,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5688,10 +5683,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45764</v>
+        <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5703,13 +5698,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5752,7 +5742,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5766,10 +5756,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45474</v>
+        <v>45730</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5782,7 +5772,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5825,7 +5815,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5839,10 +5829,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45474</v>
+        <v>45316</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5855,7 +5845,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5898,7 +5888,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5908,14 +5898,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
         <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5928,7 +5918,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5971,7 +5961,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5985,10 +5975,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45103</v>
+        <v>45179</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6000,8 +5990,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6044,7 +6039,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6058,10 +6053,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45537</v>
+        <v>44691</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6073,8 +6068,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6117,7 +6117,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45576</v>
+        <v>45001</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6146,13 +6146,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>9.300000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6195,7 +6190,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6209,10 +6204,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44852</v>
+        <v>44628</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6225,7 +6220,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6268,7 +6263,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6282,10 +6277,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45191</v>
+        <v>45882</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6299,11 +6294,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6346,7 +6341,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6356,14 +6351,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45320</v>
+        <v>45729</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6376,7 +6371,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6419,7 +6414,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6433,10 +6428,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45089</v>
+        <v>45882</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6448,8 +6443,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6502,14 +6502,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45154</v>
+        <v>44480</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45169</v>
+        <v>45405</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6594,13 +6594,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6643,7 +6638,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6657,10 +6652,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44992</v>
+        <v>45769</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6672,8 +6667,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44973</v>
+        <v>45554</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45607</v>
+        <v>45169</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6818,8 +6818,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6862,7 +6867,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6876,10 +6881,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45918</v>
+        <v>44860</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6892,7 +6897,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6935,7 +6940,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6949,10 +6954,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45089</v>
+        <v>45918</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6965,7 +6970,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7008,7 +7013,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7022,10 +7027,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45588</v>
+        <v>45232</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7037,8 +7042,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7081,7 +7091,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7095,10 +7105,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45028</v>
+        <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7111,7 +7121,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7154,7 +7164,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7164,14 +7174,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45056</v>
+        <v>45598</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7183,8 +7193,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7227,7 +7242,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7241,10 +7256,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45567</v>
+        <v>45631</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7257,7 +7272,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7300,7 +7315,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7314,10 +7329,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45063</v>
+        <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7330,7 +7345,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7373,7 +7388,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7387,10 +7402,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45408</v>
+        <v>45937</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7402,13 +7417,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7451,7 +7461,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7468,7 +7478,7 @@
         <v>45937</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7481,7 +7491,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7524,7 +7534,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7538,10 +7548,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45937</v>
+        <v>45205</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7553,8 +7563,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7597,7 +7612,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7611,10 +7626,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45205</v>
+        <v>45191</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7628,11 +7643,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7675,7 +7690,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7689,10 +7704,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45405</v>
+        <v>45966</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7705,7 +7720,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7748,7 +7763,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7762,10 +7777,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45155</v>
+        <v>45597</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7777,13 +7792,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7826,7 +7836,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7840,10 +7850,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44973</v>
+        <v>45537</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7855,13 +7865,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7904,7 +7909,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7918,10 +7923,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45121</v>
+        <v>45978</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7931,6 +7936,11 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -7977,7 +7987,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7991,10 +8001,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44628</v>
+        <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8007,7 +8017,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8050,7 +8060,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8060,14 +8070,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45440</v>
+        <v>46142</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8080,7 +8090,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8123,7 +8133,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8137,10 +8147,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45196</v>
+        <v>45989</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8152,13 +8162,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8201,7 +8206,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8215,10 +8220,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45966</v>
+        <v>46146</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8230,8 +8235,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>12.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8274,7 +8284,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8288,10 +8298,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45613</v>
+        <v>46148</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8304,7 +8314,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8347,7 +8357,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8361,10 +8371,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45607</v>
+        <v>46148</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8377,7 +8387,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8420,7 +8430,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8430,14 +8440,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45363</v>
+        <v>45607</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8450,7 +8460,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8493,7 +8503,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8507,10 +8517,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45232</v>
+        <v>46149</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8522,13 +8532,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8571,7 +8576,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8585,10 +8590,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45639</v>
+        <v>45964</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8601,7 +8606,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8644,7 +8649,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8658,10 +8663,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45978</v>
+        <v>46153</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8675,11 +8680,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8722,7 +8727,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8736,10 +8741,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45408</v>
+        <v>46153</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8753,11 +8758,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8800,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8814,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45699</v>
+        <v>45764</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8829,8 +8834,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8873,7 +8883,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8887,10 +8897,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45989</v>
+        <v>46006</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8903,7 +8913,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8946,7 +8956,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8960,10 +8970,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45825</v>
+        <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8976,7 +8986,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9019,7 +9029,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9033,10 +9043,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45169</v>
+        <v>44852</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9048,13 +9058,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9097,7 +9102,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9111,10 +9116,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45827</v>
+        <v>44973</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9126,13 +9131,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9175,7 +9175,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45964</v>
+        <v>46014</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9248,7 +9248,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45631</v>
+        <v>46014</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.7</v>
+        <v>22.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45155</v>
+        <v>46020</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9350,13 +9350,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9399,7 +9394,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9409,14 +9404,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45679</v>
+        <v>45320</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9429,7 +9424,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9472,7 +9467,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9482,14 +9477,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46006</v>
+        <v>45974</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9502,7 +9497,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9545,7 +9540,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9559,10 +9554,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45226</v>
+        <v>45454</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9574,13 +9569,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9623,7 +9613,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9637,10 +9627,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45730</v>
+        <v>45454</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9653,7 +9643,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9696,7 +9686,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9710,10 +9700,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46008</v>
+        <v>46045</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9726,7 +9716,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9769,7 +9759,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9779,14 +9769,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45049</v>
+        <v>45769</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9799,7 +9789,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9842,7 +9832,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9856,10 +9846,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46014</v>
+        <v>45408</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9871,8 +9861,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9915,7 +9910,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9929,10 +9924,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46014</v>
+        <v>45056</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9988,7 +9983,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10002,10 +9997,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46045</v>
+        <v>45155</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10017,8 +10012,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10061,7 +10061,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10071,14 +10071,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46020</v>
+        <v>45056</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10134,7 +10134,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10144,14 +10144,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46238</v>
+        <v>45639</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10207,7 +10207,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45631</v>
+        <v>45994</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10236,8 +10236,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10280,7 +10285,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10290,14 +10295,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45274</v>
+        <v>45474</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10310,7 +10315,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10353,7 +10358,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10363,14 +10368,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45994</v>
+        <v>45588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10382,13 +10387,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10431,7 +10431,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45769</v>
+        <v>44973</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10509,7 +10509,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45769</v>
+        <v>46176</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10540,11 +10540,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10587,7 +10587,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10601,10 +10601,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46246</v>
+        <v>46093</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10660,7 +10660,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10674,10 +10674,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45001</v>
+        <v>46093</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>22.4</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10733,7 +10733,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10747,10 +10747,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45586</v>
+        <v>45034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10762,8 +10762,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>3.3</v>
+        <v>8.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10806,7 +10811,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10820,10 +10825,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46266</v>
+        <v>46099</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10841,7 +10846,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10884,7 +10889,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10898,10 +10903,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45607</v>
+        <v>46105</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10914,7 +10919,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10957,7 +10962,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10971,10 +10976,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45200</v>
+        <v>46105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10986,13 +10991,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11035,7 +11035,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11049,10 +11049,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11064,8 +11064,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11108,7 +11113,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11122,10 +11127,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46093</v>
+        <v>46108</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11137,8 +11142,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11181,7 +11191,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11195,10 +11205,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46099</v>
+        <v>46189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11216,7 +11226,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>13.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11259,7 +11269,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11273,10 +11283,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11288,8 +11298,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11332,7 +11347,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11346,10 +11361,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46105</v>
+        <v>46114</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11361,8 +11376,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11405,7 +11425,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11419,10 +11439,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11440,7 +11460,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11483,7 +11503,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11497,10 +11517,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45560</v>
+        <v>46189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11514,11 +11534,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11561,7 +11581,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11575,10 +11595,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46108</v>
+        <v>46190</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11596,7 +11616,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11639,7 +11659,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11653,10 +11673,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11674,7 +11694,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11717,7 +11737,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11731,10 +11751,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46113</v>
+        <v>45155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11748,11 +11768,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11795,7 +11815,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11809,10 +11829,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46114</v>
+        <v>45474</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11824,13 +11844,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11873,7 +11888,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11887,10 +11902,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46119</v>
+        <v>45613</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11902,13 +11917,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11951,7 +11961,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11965,10 +11975,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45056</v>
+        <v>46153</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11980,8 +11990,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12024,7 +12039,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12038,10 +12053,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45233</v>
+        <v>45408</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12059,7 +12074,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12102,7 +12117,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12116,10 +12131,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45454</v>
+        <v>45169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12131,8 +12146,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12175,7 +12195,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12189,10 +12209,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45454</v>
+        <v>45560</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12204,8 +12224,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12248,7 +12273,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12262,10 +12287,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44727</v>
+        <v>45200</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12279,11 +12304,11 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12326,7 +12351,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12340,10 +12365,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45882</v>
+        <v>45769</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12361,7 +12386,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12404,7 +12429,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12418,10 +12443,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45882</v>
+        <v>45089</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12433,13 +12458,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12482,7 +12502,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12499,7 +12519,7 @@
         <v>45588</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12512,7 +12532,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12555,7 +12575,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12569,10 +12589,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45179</v>
+        <v>45632</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12586,11 +12606,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12633,7 +12653,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12643,14 +12663,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45607</v>
+        <v>45063</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12663,7 +12683,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12706,7 +12726,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12716,14 +12736,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44480</v>
+        <v>45607</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12736,7 +12756,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12779,7 +12799,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12793,10 +12813,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45554</v>
+        <v>45049</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12809,7 +12829,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12852,7 +12872,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12862,14 +12882,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45769</v>
+        <v>46258</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12881,8 +12901,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12925,7 +12950,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12939,10 +12964,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45169</v>
+        <v>44523</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12954,13 +12979,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13003,7 +13023,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13017,10 +13037,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45598</v>
+        <v>45405</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13032,13 +13052,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4</v>
+        <v>7.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13081,7 +13096,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13095,10 +13110,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45316</v>
+        <v>45233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13110,8 +13125,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13154,7 +13174,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13168,10 +13188,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45567</v>
+        <v>46265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13183,8 +13203,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13227,7 +13252,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13241,10 +13266,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45632</v>
+        <v>46265</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13258,11 +13283,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13305,7 +13330,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13319,10 +13344,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44691</v>
+        <v>46223</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13334,13 +13359,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13383,7 +13403,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13397,10 +13417,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45729</v>
+        <v>45121</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13413,7 +13433,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13456,7 +13476,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13470,10 +13490,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45597</v>
+        <v>46268</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13485,8 +13505,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13529,7 +13554,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13539,14 +13564,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46142</v>
+        <v>45028</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13559,7 +13584,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13602,7 +13627,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13616,10 +13641,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45034</v>
+        <v>46268</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13633,11 +13658,11 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13680,7 +13705,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13694,10 +13719,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44992</v>
+        <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13709,8 +13734,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13753,7 +13783,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13767,10 +13797,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46146</v>
+        <v>46197</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13784,11 +13814,11 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>12.1</v>
+        <v>1.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13831,7 +13861,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13845,10 +13875,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46148</v>
+        <v>45089</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13904,7 +13934,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13918,10 +13948,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46148</v>
+        <v>46253</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13934,7 +13964,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13977,7 +14007,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13991,10 +14021,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46149</v>
+        <v>45567</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14007,7 +14037,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14050,7 +14080,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14064,10 +14094,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46153</v>
+        <v>46232</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14079,13 +14109,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14128,7 +14153,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14142,10 +14167,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45191</v>
+        <v>44727</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14163,7 +14188,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14206,7 +14231,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14216,14 +14241,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45196</v>
+        <v>46232</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14241,7 +14266,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14284,7 +14309,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14298,10 +14323,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46153</v>
+        <v>45607</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14313,13 +14338,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14362,7 +14382,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14372,14 +14392,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45974</v>
+        <v>46233</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14391,8 +14411,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14435,7 +14460,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14449,10 +14474,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46176</v>
+        <v>44992</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14464,13 +14489,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14513,7 +14533,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14527,10 +14547,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46189</v>
+        <v>45169</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14548,7 +14568,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>13.7</v>
+        <v>5.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14591,7 +14611,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14605,10 +14625,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46189</v>
+        <v>45169</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14626,7 +14646,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14669,7 +14689,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14679,14 +14699,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46190</v>
+        <v>46238</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14698,13 +14718,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14747,7 +14762,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14761,10 +14776,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46153</v>
+        <v>45440</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14776,13 +14791,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14825,7 +14835,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14839,10 +14849,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46247</v>
+        <v>45191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14856,11 +14866,11 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14903,7 +14913,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14917,10 +14927,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46258</v>
+        <v>45196</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14934,11 +14944,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14981,7 +14991,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14995,10 +15005,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46265</v>
+        <v>45390</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15010,13 +15020,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15059,7 +15064,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15073,10 +15078,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46223</v>
+        <v>45792</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15088,8 +15093,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15132,7 +15142,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15146,10 +15156,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46265</v>
+        <v>46246</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15161,13 +15171,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15210,7 +15215,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15224,10 +15229,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46268</v>
+        <v>45792</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15241,11 +15246,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>8.9</v>
+        <v>3.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15288,7 +15293,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15302,10 +15307,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46268</v>
+        <v>45586</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15317,13 +15322,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15366,7 +15366,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15380,10 +15380,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46197</v>
+        <v>45576</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15397,11 +15397,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15444,7 +15444,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15458,10 +15458,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46197</v>
+        <v>46247</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15522,7 +15522,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15536,10 +15536,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46253</v>
+        <v>46266</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15551,8 +15551,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15595,7 +15600,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15605,14 +15610,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46232</v>
+        <v>45274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15624,13 +15629,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15673,7 +15673,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15687,10 +15687,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46232</v>
+        <v>45825</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15746,7 +15746,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15760,10 +15760,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46233</v>
+        <v>45827</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15777,11 +15777,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>44585</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>46085</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 62471-2023</t>
+          <t>A 31484-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45268</v>
+        <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.3</v>
+        <v>11.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -894,151 +894,151 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Bårdlav
+Korallblylav
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 31484-2026 artfynd.xlsx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 31484-2026 karta.png", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 31484-2026 georefererad karta.tif", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 31484-2026 FSC-klagomål.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 31484-2026 FSC-klagomål mail.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 31484-2026 tillsynsbegäran.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 31484-2026 tillsynsbegäran mail.docx", "A 31484-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 62471-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Kryddspindling
 Orange taggsvamp
 Zontaggsvamp</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 62471-2023 artfynd.xlsx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 62471-2023 karta.png", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 62471-2023 georefererad karta.tif", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 62471-2023 FSC-klagomål.docx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 62471-2023 FSC-klagomål mail.docx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 62471-2023 tillsynsbegäran.docx", "A 62471-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 62471-2023 tillsynsbegäran mail.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 31484-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Bårdlav
-Korallblylav
-Rävticka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 31484-2026 artfynd.xlsx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 31484-2026 karta.png", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 31484-2026 georefererad karta.tif", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 31484-2026 FSC-klagomål.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 31484-2026 FSC-klagomål mail.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 31484-2026 tillsynsbegäran.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 31484-2026 tillsynsbegäran mail.docx", "A 31484-2026")</f>
         <v/>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 63777-2025</t>
+          <t>A 15262-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46019</v>
+        <v>46105</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1218,376 +1218,376 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Brunklöver
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 55711-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45622</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Persiljespindling
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U9" t="n">
         <v>8</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63777-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.4</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>8</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>8</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 15262-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55711-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45622</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Persiljespindling
-Skogsknipprot</t>
-        </is>
-      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33377-2023</t>
+          <t>A 36009-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45128</v>
+        <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1658,151 +1658,151 @@
         <v>2</v>
       </c>
       <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 33377-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45128</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Gul taggsvamp
 Dofttaggsvamp</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 33377-2023 artfynd.xlsx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 33377-2023 karta.png", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 33377-2023 georefererad karta.tif", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 33377-2023 FSC-klagomål.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 33377-2023 FSC-klagomål mail.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 33377-2023 tillsynsbegäran.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 33377-2023 tillsynsbegäran mail.docx", "A 33377-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 36009-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56936-2021</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44480</v>
+        <v>45773</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1943,14 +1943,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1984,42 +1989,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2033,10 +2038,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45773</v>
+        <v>44873</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2048,19 +2053,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2090,46 +2090,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45744</v>
+        <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2200,46 +2200,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45882</v>
+        <v>46139</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2268,16 +2268,11 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>15.5</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2298,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,46 +2305,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 56936-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2359,14 +2358,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45644</v>
+        <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,7 +2378,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2415,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2423,38 +2422,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2468,10 +2467,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46139</v>
+        <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2483,14 +2482,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2517,53 +2521,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 28307-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45142</v>
+        <v>46196</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2594,20 +2594,20 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2638,42 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45762</v>
+        <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2704,86 +2704,86 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>15.5</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28307-2026</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46196</v>
+        <v>45744</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2854,46 +2854,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44873</v>
+        <v>46268</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,14 +2922,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2963,42 +2968,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46268</v>
+        <v>46253</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,13 +3032,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3073,42 +3073,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3125,7 +3125,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3182,38 +3182,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 38927-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46253</v>
+        <v>46282</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -3283,42 +3283,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38927-2026</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46282</v>
+        <v>45644</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3348,13 +3348,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3388,35 +3388,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
         <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44860</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44600</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>44849</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45196</v>
+        <v>45405</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4875,13 +4875,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45699</v>
+        <v>44860</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5027,7 +5022,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45607</v>
+        <v>45474</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44552</v>
+        <v>46014</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5226,14 +5221,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45155</v>
+        <v>45320</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5245,13 +5240,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5294,7 +5284,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5308,10 +5298,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45363</v>
+        <v>46020</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5324,7 +5314,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5384,7 +5374,7 @@
         <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5440,7 +5430,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5454,10 +5444,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45226</v>
+        <v>45274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5469,13 +5459,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5518,7 +5503,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5532,10 +5517,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45705</v>
+        <v>45169</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5547,8 +5532,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5591,7 +5581,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5605,10 +5595,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45200</v>
+        <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5622,11 +5612,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5669,7 +5659,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5683,10 +5673,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45567</v>
+        <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5699,7 +5689,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5742,7 +5732,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5756,10 +5746,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45730</v>
+        <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5772,7 +5762,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5815,7 +5805,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5829,10 +5819,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45316</v>
+        <v>46045</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5845,7 +5835,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5888,7 +5878,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5902,10 +5892,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45274</v>
+        <v>45056</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5918,7 +5908,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5961,7 +5951,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5975,10 +5965,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45179</v>
+        <v>45408</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5996,7 +5986,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6039,7 +6029,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6053,10 +6043,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44691</v>
+        <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6068,13 +6058,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6117,7 +6102,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6127,14 +6112,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45001</v>
+        <v>45994</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6146,8 +6131,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>22.4</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6190,7 +6180,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6204,10 +6194,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44628</v>
+        <v>45405</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6220,7 +6210,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6263,7 +6253,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6277,10 +6267,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45882</v>
+        <v>45155</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6294,11 +6284,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6341,7 +6331,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6355,10 +6345,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45729</v>
+        <v>44973</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6370,8 +6360,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6414,7 +6409,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6428,10 +6423,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45882</v>
+        <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6443,13 +6438,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6492,7 +6482,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6502,14 +6492,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44480</v>
+        <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6522,7 +6512,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6565,7 +6555,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6579,10 +6569,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45405</v>
+        <v>46093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6595,7 +6585,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6638,7 +6628,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6652,10 +6642,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45769</v>
+        <v>46093</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6667,13 +6657,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6716,7 +6701,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6730,10 +6715,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45554</v>
+        <v>46099</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6745,8 +6730,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6789,7 +6779,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6803,10 +6793,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45169</v>
+        <v>46105</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6818,13 +6808,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6867,7 +6852,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6881,10 +6866,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44860</v>
+        <v>46105</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6897,7 +6882,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6940,7 +6925,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6954,10 +6939,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45918</v>
+        <v>46105</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6969,8 +6954,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>7.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7013,7 +7003,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7027,10 +7017,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45232</v>
+        <v>45613</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7042,13 +7032,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7091,7 +7076,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7105,10 +7090,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45679</v>
+        <v>46108</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7120,8 +7105,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7164,7 +7154,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7178,10 +7168,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45598</v>
+        <v>45607</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7193,13 +7183,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7242,7 +7227,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7256,10 +7241,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45631</v>
+        <v>45363</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7315,7 +7300,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7329,10 +7314,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44992</v>
+        <v>46111</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7344,8 +7329,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>8.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7388,7 +7378,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7402,10 +7392,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45937</v>
+        <v>46113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7417,8 +7407,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7461,7 +7456,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7475,10 +7470,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45937</v>
+        <v>46114</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7490,8 +7485,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7534,7 +7534,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45205</v>
+        <v>46119</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45191</v>
+        <v>45966</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7641,13 +7641,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7690,7 +7685,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7704,10 +7699,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7719,8 +7714,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45597</v>
+        <v>45631</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45537</v>
+        <v>45989</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45978</v>
+        <v>45964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7938,13 +7938,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7987,7 +7982,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8001,10 +7996,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45103</v>
+        <v>45169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8016,8 +8011,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8060,7 +8060,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8070,14 +8070,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46142</v>
+        <v>45705</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8133,7 +8133,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45989</v>
+        <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8206,7 +8206,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46146</v>
+        <v>44552</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8235,13 +8235,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>12.1</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8284,7 +8279,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8298,10 +8293,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46148</v>
+        <v>45554</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8314,7 +8309,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8357,7 +8352,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8371,10 +8366,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46148</v>
+        <v>46006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8387,7 +8382,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8430,7 +8425,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8440,14 +8435,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45607</v>
+        <v>45169</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8459,8 +8454,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46149</v>
+        <v>45155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8532,8 +8532,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8576,7 +8581,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8590,10 +8595,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45964</v>
+        <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8606,7 +8611,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8649,7 +8654,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8663,10 +8668,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46153</v>
+        <v>45598</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8680,11 +8685,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8727,7 +8732,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8741,10 +8746,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46153</v>
+        <v>46014</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8756,13 +8761,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>22.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45764</v>
+        <v>45200</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46006</v>
+        <v>45764</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8912,8 +8912,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8956,7 +8961,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8970,10 +8975,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46008</v>
+        <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8986,7 +8991,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9029,7 +9034,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9043,10 +9048,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44852</v>
+        <v>45474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9059,7 +9064,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9102,7 +9107,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9112,14 +9117,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44973</v>
+        <v>46142</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9132,7 +9137,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9175,7 +9180,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9189,10 +9194,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46014</v>
+        <v>45827</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9204,8 +9209,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9248,7 +9258,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9262,10 +9272,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46014</v>
+        <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9277,8 +9287,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>22.8</v>
+        <v>12.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9321,7 +9336,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9335,10 +9350,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46020</v>
+        <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9351,7 +9366,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9394,7 +9409,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9404,14 +9419,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45320</v>
+        <v>46148</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9424,7 +9439,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9467,7 +9482,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9477,14 +9492,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45974</v>
+        <v>46149</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9497,7 +9512,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9540,7 +9555,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9554,10 +9569,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45454</v>
+        <v>46153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9569,8 +9584,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9613,7 +9633,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 21983-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9627,10 +9647,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45454</v>
+        <v>46153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9640,6 +9660,11 @@
       <c r="G110" t="inlineStr">
         <is>
           <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -9686,7 +9711,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9700,10 +9725,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46045</v>
+        <v>45103</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9716,7 +9741,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9759,7 +9784,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9769,14 +9794,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45769</v>
+        <v>45537</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9789,7 +9814,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9832,7 +9857,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9842,14 +9867,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45408</v>
+        <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9861,13 +9886,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9910,7 +9930,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9924,10 +9944,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45056</v>
+        <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9940,7 +9960,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9983,7 +10003,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9997,10 +10017,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45155</v>
+        <v>45191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10014,11 +10034,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10061,7 +10081,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10071,14 +10091,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45056</v>
+        <v>45089</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10091,7 +10111,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10134,7 +10154,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10148,10 +10168,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45639</v>
+        <v>44992</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10164,7 +10184,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10207,7 +10227,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10217,14 +10237,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45994</v>
+        <v>45607</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10236,13 +10256,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10285,7 +10300,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10299,10 +10314,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45474</v>
+        <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10314,8 +10329,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10358,7 +10378,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10375,7 +10395,7 @@
         <v>45588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10388,7 +10408,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10431,7 +10451,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10445,10 +10465,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44973</v>
+        <v>45028</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10460,13 +10480,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10509,7 +10524,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10523,10 +10538,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46176</v>
+        <v>45567</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10538,13 +10553,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10587,7 +10597,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10601,10 +10611,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46093</v>
+        <v>46189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10616,8 +10626,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>3.6</v>
+        <v>13.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10660,7 +10675,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10674,10 +10689,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46093</v>
+        <v>45063</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10690,7 +10705,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10733,7 +10748,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10747,10 +10762,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45034</v>
+        <v>46189</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10764,11 +10779,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10811,7 +10826,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10825,10 +10840,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46099</v>
+        <v>46190</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10846,7 +10861,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10889,7 +10904,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10903,10 +10918,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46105</v>
+        <v>45205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10918,8 +10933,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10962,7 +10982,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10976,10 +10996,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46105</v>
+        <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10991,8 +11011,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11035,7 +11060,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11049,10 +11074,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46105</v>
+        <v>45882</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11066,11 +11091,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11113,7 +11138,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11127,10 +11152,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46108</v>
+        <v>45121</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11140,11 +11165,6 @@
       <c r="G130" t="inlineStr">
         <is>
           <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -11191,7 +11211,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11205,10 +11225,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46189</v>
+        <v>46153</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11222,11 +11242,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>13.7</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11269,7 +11289,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11283,10 +11303,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46111</v>
+        <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11298,13 +11318,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11347,7 +11362,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11361,10 +11376,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46114</v>
+        <v>45440</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11376,13 +11391,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11425,7 +11435,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11439,10 +11449,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46113</v>
+        <v>45196</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11456,11 +11466,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11503,7 +11513,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11517,10 +11527,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46189</v>
+        <v>46258</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11538,7 +11548,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11581,7 +11591,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11595,10 +11605,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46190</v>
+        <v>45232</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11616,7 +11626,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11659,7 +11669,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11673,10 +11683,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46119</v>
+        <v>45639</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11688,13 +11698,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11737,7 +11742,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11751,10 +11756,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45155</v>
+        <v>45408</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11768,11 +11773,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11815,7 +11820,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11829,10 +11834,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45474</v>
+        <v>45699</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11845,7 +11850,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11888,7 +11893,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11902,10 +11907,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45613</v>
+        <v>45169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11917,8 +11922,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11961,7 +11971,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11975,10 +11985,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46153</v>
+        <v>45155</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11996,7 +12006,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12039,7 +12049,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12053,10 +12063,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45408</v>
+        <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12074,7 +12084,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12117,7 +12127,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12131,10 +12141,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45169</v>
+        <v>46223</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12146,13 +12156,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12195,7 +12200,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12209,10 +12214,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45560</v>
+        <v>45679</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12224,13 +12229,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12273,7 +12273,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45200</v>
+        <v>46265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12351,7 +12351,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12365,10 +12365,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45769</v>
+        <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12382,11 +12382,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>8.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12429,7 +12429,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12443,10 +12443,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45089</v>
+        <v>46268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12458,8 +12458,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12502,7 +12507,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12516,10 +12521,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45588</v>
+        <v>45226</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12531,8 +12536,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12575,7 +12585,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12589,10 +12599,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45632</v>
+        <v>45730</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12604,13 +12614,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12653,7 +12658,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12667,10 +12672,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45063</v>
+        <v>45049</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12683,7 +12688,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12726,7 +12731,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12740,10 +12745,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45607</v>
+        <v>46197</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12755,8 +12760,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.1</v>
+        <v>4.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12799,7 +12809,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12813,10 +12823,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45049</v>
+        <v>46197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12828,8 +12838,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12872,7 +12887,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12886,10 +12901,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12901,13 +12916,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12950,7 +12960,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12960,14 +12970,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44523</v>
+        <v>46232</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12979,8 +12989,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13023,7 +13038,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13037,10 +13052,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45405</v>
+        <v>46232</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13053,7 +13068,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13096,7 +13111,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13110,10 +13125,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45233</v>
+        <v>46233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13131,7 +13146,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13174,7 +13189,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13188,10 +13203,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46265</v>
+        <v>45631</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13203,13 +13218,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13252,7 +13262,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13262,14 +13272,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46265</v>
+        <v>45274</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13281,13 +13291,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13330,7 +13335,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13340,14 +13345,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13360,7 +13365,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>9.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13403,7 +13408,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13417,10 +13422,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45121</v>
+        <v>45769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13432,8 +13437,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13476,7 +13486,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13490,10 +13500,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46268</v>
+        <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13507,11 +13517,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13554,7 +13564,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13568,10 +13578,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45028</v>
+        <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13584,7 +13594,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>22.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13627,7 +13637,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13641,10 +13651,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46268</v>
+        <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13656,13 +13666,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13705,7 +13710,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13719,10 +13724,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46197</v>
+        <v>45586</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13734,13 +13739,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13783,7 +13783,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13797,10 +13797,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46197</v>
+        <v>46266</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13861,7 +13861,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13875,10 +13875,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45089</v>
+        <v>45607</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13934,7 +13934,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46253</v>
+        <v>45200</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13963,8 +13963,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14007,7 +14012,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14021,10 +14026,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45567</v>
+        <v>46247</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14036,8 +14041,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14080,7 +14090,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14094,10 +14104,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46232</v>
+        <v>45560</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14109,8 +14119,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14153,7 +14168,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14167,10 +14182,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44727</v>
+        <v>45056</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14182,13 +14197,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14231,7 +14241,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14241,14 +14251,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46232</v>
+        <v>45233</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14262,11 +14272,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14309,7 +14319,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14323,10 +14333,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45607</v>
+        <v>45454</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14339,7 +14349,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14382,7 +14392,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14396,10 +14406,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46233</v>
+        <v>45454</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14411,13 +14421,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14460,7 +14465,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14474,10 +14479,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44992</v>
+        <v>44727</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14489,8 +14494,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>6.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14533,7 +14543,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14547,10 +14557,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45169</v>
+        <v>45588</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14562,13 +14572,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14611,7 +14616,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14625,10 +14630,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45169</v>
+        <v>45179</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14646,7 +14651,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14689,7 +14694,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14699,14 +14704,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46238</v>
+        <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14719,7 +14724,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14762,7 +14767,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14772,14 +14777,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45440</v>
+        <v>45769</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14792,7 +14797,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14835,7 +14840,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14849,10 +14854,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45191</v>
+        <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14864,13 +14869,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14913,7 +14913,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14927,10 +14927,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45196</v>
+        <v>45567</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14942,13 +14942,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14991,7 +14986,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15005,10 +15000,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45390</v>
+        <v>45632</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15020,8 +15015,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15064,7 +15064,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15078,10 +15078,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45792</v>
+        <v>44691</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15142,7 +15142,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15156,10 +15156,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46246</v>
+        <v>45729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45792</v>
+        <v>45597</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15244,13 +15244,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15293,7 +15288,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15307,10 +15302,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45586</v>
+        <v>45034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15322,8 +15317,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>3.3</v>
+        <v>8.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15366,7 +15366,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15380,10 +15380,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45576</v>
+        <v>44992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15395,13 +15395,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15444,7 +15439,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15458,10 +15453,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46247</v>
+        <v>45191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15475,11 +15470,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15522,7 +15517,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15536,10 +15531,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46266</v>
+        <v>45196</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15553,11 +15548,11 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15600,7 +15595,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15614,10 +15609,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45274</v>
+        <v>45390</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15630,7 +15625,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15673,7 +15668,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15687,10 +15682,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45825</v>
+        <v>45792</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15702,8 +15697,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15746,7 +15746,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15760,10 +15760,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45827</v>
+        <v>45792</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>44585</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>46085</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>46105</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45622</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45091</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45773</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44873</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46139</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46196</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45744</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>46268</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46253</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>46282</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45644</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44860</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44600</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>44849</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45405</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44860</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45474</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46014</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45320</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>46020</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45169</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>46045</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45056</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45408</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45994</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>45405</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>45155</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44973</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>46093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>46093</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>46099</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>46105</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46105</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>46105</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45613</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>46108</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>45607</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45363</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>46111</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>46113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>46114</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46119</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45966</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45631</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45989</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45705</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44552</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45554</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>46006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45169</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45598</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>46014</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>45200</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45764</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46142</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45827</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46148</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>46149</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>46153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45103</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45537</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>45089</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44992</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45607</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45028</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45567</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45063</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46189</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>46190</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45882</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45121</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46153</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45440</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45196</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>46258</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45232</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45639</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45408</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45699</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45155</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46223</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45679</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>46265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45226</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45730</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45049</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>46197</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>46197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46253</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>46232</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>46232</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>46233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45631</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45274</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46238</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45586</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>46266</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45607</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45200</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>46247</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45560</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45056</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45233</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45454</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45454</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44727</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45588</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>45179</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45769</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>45567</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45632</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44691</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45597</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45196</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45390</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45792</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>45792</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44585</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>46085</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45268</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>46105</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45622</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45091</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45773</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44873</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45142</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>46139</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44480</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>46196</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45744</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>46268</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46253</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>46282</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45644</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44860</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44600</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>44849</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45405</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44860</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45474</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>46014</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45320</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>46020</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45154</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45169</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>46045</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45056</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45408</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45994</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>45405</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>45155</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>44973</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>45937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>46093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>46093</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>46099</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>46105</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46105</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>46105</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45613</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>46108</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>45607</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45363</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>46111</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>46113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>46114</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46119</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45966</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45631</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45989</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45705</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44552</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45554</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>46006</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45169</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45598</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>46014</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>45200</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45764</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46142</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45827</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46148</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>46149</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>46153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45103</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45537</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>44852</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>45089</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44992</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45607</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45028</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45567</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45063</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46189</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>46190</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45882</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45121</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46153</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45440</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45196</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>46258</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45232</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45639</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45408</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45699</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45155</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46223</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45679</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>46265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45226</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45730</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45049</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>46197</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>46197</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46253</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>46232</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>46232</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>46233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45631</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45274</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46238</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45586</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>46266</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45607</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45200</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>46247</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45560</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45056</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45233</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45454</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45454</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44727</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45588</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>45179</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45769</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>45567</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45632</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44691</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45597</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45196</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45390</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45792</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>45792</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44585</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>46085</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE194"/>
+  <dimension ref="A1:AE193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31484-2026</t>
+          <t>A 62471-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46223</v>
+        <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11.7</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -894,151 +894,151 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Kryddspindling
+Orange taggsvamp
+Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 62471-2023 artfynd.xlsx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 62471-2023 karta.png", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 62471-2023 georefererad karta.tif", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 62471-2023 FSC-klagomål.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 62471-2023 FSC-klagomål mail.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 62471-2023 tillsynsbegäran.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 62471-2023 tillsynsbegäran mail.docx", "A 62471-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31484-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Bårdlav
 Korallblylav
 Rävticka</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 31484-2026 artfynd.xlsx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 31484-2026 karta.png", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 31484-2026 georefererad karta.tif", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 31484-2026 FSC-klagomål.docx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 31484-2026 FSC-klagomål mail.docx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 31484-2026 tillsynsbegäran.docx", "A 31484-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 31484-2026 tillsynsbegäran mail.docx", "A 31484-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 62471-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45268</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Kryddspindling
-Orange taggsvamp
-Zontaggsvamp</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 62471-2023 artfynd.xlsx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 62471-2023 karta.png", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 62471-2023 georefererad karta.tif", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 62471-2023 FSC-klagomål.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 62471-2023 FSC-klagomål mail.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 62471-2023 tillsynsbegäran.docx", "A 62471-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 62471-2023 tillsynsbegäran mail.docx", "A 62471-2023")</f>
         <v/>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>46105</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 55711-2024</t>
+          <t>A 63777-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45622</v>
+        <v>46019</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1291,16 +1291,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1324,270 +1324,270 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 55711-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45622</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Persiljespindling
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>8</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63777-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46019</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 36009-2026</t>
+          <t>A 33377-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46266</v>
+        <v>45128</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1622,34 +1622,34 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>8.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="R11" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1658,151 +1658,151 @@
         <v>2</v>
       </c>
       <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp
+Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 33377-2023 artfynd.xlsx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 33377-2023 karta.png", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 33377-2023 georefererad karta.tif", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 33377-2023 FSC-klagomål.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 33377-2023 FSC-klagomål mail.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 33377-2023 tillsynsbegäran.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 33377-2023 tillsynsbegäran mail.docx", "A 33377-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 36009-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Gullviva</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 33377-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45128</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Gul taggsvamp
-Dofttaggsvamp</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 33377-2023 artfynd.xlsx", "A 33377-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 33377-2023 karta.png", "A 33377-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 33377-2023 georefererad karta.tif", "A 33377-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 33377-2023 FSC-klagomål.docx", "A 33377-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 33377-2023 FSC-klagomål mail.docx", "A 33377-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 33377-2023 tillsynsbegäran.docx", "A 33377-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 33377-2023 tillsynsbegäran mail.docx", "A 33377-2023")</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20257-2025</t>
+          <t>A 56936-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45773</v>
+        <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1943,19 +1943,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1989,42 +1984,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52063-2022</t>
+          <t>A 20257-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44873</v>
+        <v>45773</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,14 +2048,19 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2090,46 +2090,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20257-2025 artfynd.xlsx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20257-2025 karta.png", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20257-2025 georefererad karta.tif", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20257-2025 FSC-klagomål.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20257-2025 FSC-klagomål mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20257-2025 tillsynsbegäran.docx", "A 20257-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20257-2025 tillsynsbegäran mail.docx", "A 20257-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34967-2023</t>
+          <t>A 15107-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45142</v>
+        <v>45744</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2160,20 +2160,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2200,46 +2200,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20407-2026</t>
+          <t>A 38017-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46139</v>
+        <v>45882</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2268,24 +2268,29 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>15.5</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -2293,10 +2298,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2305,50 +2310,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56936-2021</t>
+          <t>A 61099-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2358,14 +2359,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44480</v>
+        <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2378,7 +2379,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2414,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2422,38 +2423,38 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 56936-2021 artfynd.xlsx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 56936-2021 karta.png", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 56936-2021 georefererad karta.tif", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 56936-2021 FSC-klagomål.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 56936-2021 FSC-klagomål mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 56936-2021 tillsynsbegäran.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 56936-2021 tillsynsbegäran mail.docx", "A 56936-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18464-2025</t>
+          <t>A 34967-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2467,10 +2468,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45762</v>
+        <v>45142</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,35 +2485,35 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2521,49 +2522,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34967-2023 artfynd.xlsx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34967-2023 karta.png", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34967-2023 georefererad karta.tif", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34967-2023 FSC-klagomål.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34967-2023 FSC-klagomål mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34967-2023 tillsynsbegäran.docx", "A 34967-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34967-2023 tillsynsbegäran mail.docx", "A 34967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28307-2026</t>
+          <t>A 20407-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,10 +2578,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46196</v>
+        <v>46139</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2592,19 +2593,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2638,42 +2634,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 20407-2026 artfynd.xlsx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 20407-2026 karta.png", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 20407-2026 georefererad karta.tif", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 20407-2026 FSC-klagomål.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 20407-2026 FSC-klagomål mail.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 20407-2026 tillsynsbegäran.docx", "A 20407-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 20407-2026 tillsynsbegäran mail.docx", "A 20407-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 20407-2026 prioriterade fågelarter.docx", "A 20407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38017-2025</t>
+          <t>A 18464-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45882</v>
+        <v>45762</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2704,17 +2704,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>15.5</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2732,58 +2732,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38017-2025 artfynd.xlsx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 18464-2025 artfynd.xlsx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38017-2025 karta.png", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 18464-2025 karta.png", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38017-2025 georefererad karta.tif", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 18464-2025 georefererad karta.tif", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38017-2025 FSC-klagomål.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 18464-2025 FSC-klagomål.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38017-2025 FSC-klagomål mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 18464-2025 FSC-klagomål mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38017-2025 tillsynsbegäran.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 18464-2025 tillsynsbegäran.docx", "A 18464-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38017-2025 tillsynsbegäran mail.docx", "A 38017-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 18464-2025 tillsynsbegäran mail.docx", "A 18464-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15107-2025</t>
+          <t>A 28307-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45744</v>
+        <v>46196</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2854,46 +2854,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15107-2025 artfynd.xlsx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 28307-2026 artfynd.xlsx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15107-2025 karta.png", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 28307-2026 karta.png", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15107-2025 georefererad karta.tif", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 28307-2026 georefererad karta.tif", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15107-2025 FSC-klagomål.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 28307-2026 FSC-klagomål.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15107-2025 FSC-klagomål mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 28307-2026 FSC-klagomål mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15107-2025 tillsynsbegäran.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 28307-2026 tillsynsbegäran.docx", "A 28307-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15107-2025 tillsynsbegäran mail.docx", "A 15107-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 28307-2026 tillsynsbegäran mail.docx", "A 28307-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36383-2026</t>
+          <t>A 52063-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46268</v>
+        <v>44873</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,19 +2922,14 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2968,42 +2963,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 52063-2022 artfynd.xlsx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 52063-2022 karta.png", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 52063-2022 georefererad karta.tif", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 52063-2022 FSC-klagomål.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 52063-2022 FSC-klagomål mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 52063-2022 tillsynsbegäran.docx", "A 52063-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 52063-2022 tillsynsbegäran mail.docx", "A 52063-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34234-2026</t>
+          <t>A 36383-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3032,8 +3027,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3073,42 +3073,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36383-2026 artfynd.xlsx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36383-2026 karta.png", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36383-2026 georefererad karta.tif", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36383-2026 FSC-klagomål.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36383-2026 FSC-klagomål mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36383-2026 tillsynsbegäran.docx", "A 36383-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36383-2026 tillsynsbegäran mail.docx", "A 36383-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34230-2026</t>
+          <t>A 34234-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3125,7 +3125,7 @@
         <v>46253</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3182,38 +3182,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34234-2026 artfynd.xlsx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34234-2026 karta.png", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34234-2026 georefererad karta.tif", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34234-2026 FSC-klagomål.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34234-2026 FSC-klagomål mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34234-2026 tillsynsbegäran.docx", "A 34234-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34234-2026 tillsynsbegäran mail.docx", "A 34234-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38927-2026</t>
+          <t>A 34230-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -3283,42 +3283,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 34230-2026 artfynd.xlsx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 34230-2026 karta.png", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 34230-2026 georefererad karta.tif", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 34230-2026 FSC-klagomål.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 34230-2026 FSC-klagomål mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 34230-2026 tillsynsbegäran.docx", "A 34230-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 34230-2026 tillsynsbegäran mail.docx", "A 34230-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 61099-2024</t>
+          <t>A 38927-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45644</v>
+        <v>46282</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3348,13 +3348,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3388,35 +3388,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 61099-2024 artfynd.xlsx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 38927-2026 artfynd.xlsx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 61099-2024 karta.png", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 38927-2026 karta.png", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 61099-2024 georefererad karta.tif", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 38927-2026 georefererad karta.tif", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 61099-2024 FSC-klagomål.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 38927-2026 FSC-klagomål.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 61099-2024 FSC-klagomål mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 38927-2026 FSC-klagomål mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 61099-2024 tillsynsbegäran.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 38927-2026 tillsynsbegäran.docx", "A 38927-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 61099-2024 tillsynsbegäran mail.docx", "A 61099-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 38927-2026 tillsynsbegäran mail.docx", "A 38927-2026")</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
         <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44860</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44873</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44600</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44852</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44838</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44620</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>44849</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44635</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15890-2024</t>
+          <t>A 46045-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45405</v>
+        <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4875,8 +4875,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4919,7 +4924,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50124-2022</t>
+          <t>A 6388-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4933,10 +4938,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44860</v>
+        <v>45699</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4949,7 +4954,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4992,7 +4997,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 67356-2021</t>
+          <t>A 57990-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44523</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5022,7 +5027,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5065,7 +5070,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27589-2024</t>
+          <t>A 51778-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45474</v>
+        <v>45607</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5095,7 +5100,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5138,7 +5143,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62-2026</t>
+          <t>A 73797-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5152,10 +5157,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46014</v>
+        <v>44552</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5168,7 +5173,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5211,7 +5216,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3587-2024</t>
+          <t>A 62155-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5221,14 +5226,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45320</v>
+        <v>46006</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5241,7 +5246,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5284,7 +5289,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 63907-2025</t>
+          <t>A 23433-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5298,10 +5303,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46020</v>
+        <v>45792</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5313,8 +5318,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5357,7 +5367,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36905-2023</t>
+          <t>A 23418-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5367,14 +5377,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45154</v>
+        <v>45792</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5386,8 +5396,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5430,7 +5445,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63495-2023</t>
+          <t>A 62882-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5444,10 +5459,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45274</v>
+        <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5460,7 +5475,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5503,7 +5518,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40144-2023</t>
+          <t>A 45290-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5517,10 +5532,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45169</v>
+        <v>45576</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5534,11 +5549,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5581,7 +5596,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45290-2024</t>
+          <t>A 9907-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5595,10 +5610,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45576</v>
+        <v>45363</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5610,13 +5625,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>9.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5659,7 +5669,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8746-2023</t>
+          <t>A 63495-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5673,10 +5683,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44973</v>
+        <v>45274</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5689,7 +5699,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5732,7 +5742,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25477-2023</t>
+          <t>A 37200-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5746,10 +5756,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45089</v>
+        <v>45155</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5761,8 +5771,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5805,7 +5820,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4887-2026</t>
+          <t>A 36905-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5815,14 +5830,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46045</v>
+        <v>45154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5835,7 +5850,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5878,7 +5893,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20378-2023</t>
+          <t>A 53030-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5888,14 +5903,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45056</v>
+        <v>45226</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5907,8 +5922,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5951,7 +5971,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16629-2024</t>
+          <t>A 7417-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5965,10 +5985,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45408</v>
+        <v>45705</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5980,13 +6000,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>8.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6029,7 +6044,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44884-2025</t>
+          <t>A 46864-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6043,10 +6058,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45918</v>
+        <v>45200</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6058,8 +6073,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6102,7 +6122,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60339-2025</t>
+          <t>A 43103-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6112,14 +6132,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45994</v>
+        <v>45567</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6131,13 +6151,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6180,7 +6195,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16042-2024</t>
+          <t>A 44884-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6194,10 +6209,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45405</v>
+        <v>45918</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6210,7 +6225,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6253,7 +6268,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37200-2023</t>
+          <t>A 29620-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6267,10 +6282,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45155</v>
+        <v>45825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6282,13 +6297,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6331,7 +6341,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7744-2023</t>
+          <t>A 30211-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6345,10 +6355,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44973</v>
+        <v>45827</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6366,7 +6376,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6409,7 +6419,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49001-2025</t>
+          <t>A 62-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6423,10 +6433,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45937</v>
+        <v>46014</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6439,7 +6449,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6482,7 +6492,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48997-2025</t>
+          <t>A 56-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6496,10 +6506,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45937</v>
+        <v>46014</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6512,7 +6522,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>22.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6555,7 +6565,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13465-2026</t>
+          <t>A 49001-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6569,10 +6579,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46093</v>
+        <v>45937</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6585,7 +6595,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6628,7 +6638,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13471-2026</t>
+          <t>A 48997-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6642,10 +6652,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46093</v>
+        <v>45937</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6658,7 +6668,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6701,7 +6711,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14234-2026</t>
+          <t>A 12526-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6715,10 +6725,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46099</v>
+        <v>45730</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6730,13 +6740,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6779,7 +6784,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15261-2026</t>
+          <t>A 63907-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6793,10 +6798,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46105</v>
+        <v>46020</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6809,7 +6814,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6852,7 +6857,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15263-2026</t>
+          <t>A 3131-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6866,10 +6871,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46105</v>
+        <v>45316</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6882,7 +6887,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6925,7 +6930,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15265-2026</t>
+          <t>A 63505-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6935,14 +6940,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46105</v>
+        <v>45274</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6954,13 +6959,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 53224-2024</t>
+          <t>A 54670-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45613</v>
+        <v>45966</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7076,7 +7076,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15981-2026</t>
+          <t>A 38018-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46108</v>
+        <v>45882</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7107,11 +7107,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>15</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7154,7 +7154,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51793-2024</t>
+          <t>A 42198-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45607</v>
+        <v>45179</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7183,8 +7183,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7227,7 +7232,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9907-2024</t>
+          <t>A 38019-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7241,10 +7246,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45363</v>
+        <v>45882</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7256,8 +7261,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7300,7 +7310,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16383-2026</t>
+          <t>A 19075-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7314,10 +7324,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46111</v>
+        <v>44691</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7331,11 +7341,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7378,7 +7388,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16897-2026</t>
+          <t>A 56726-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7392,10 +7402,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46113</v>
+        <v>45978</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7409,11 +7419,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7456,7 +7466,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17063-2026</t>
+          <t>A 4887-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7470,10 +7480,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46114</v>
+        <v>46045</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7485,13 +7495,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7534,7 +7539,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17318-2026</t>
+          <t>A 12796-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7548,10 +7553,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46119</v>
+        <v>45001</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7563,13 +7568,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>6.1</v>
+        <v>22.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54670-2025</t>
+          <t>A 11099-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45966</v>
+        <v>44628</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56726-2025</t>
+          <t>A 59527-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45978</v>
+        <v>45989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7714,13 +7714,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7763,7 +7758,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57993-2024</t>
+          <t>A 54143-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7777,10 +7772,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45631</v>
+        <v>45964</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7793,7 +7788,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7836,7 +7831,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59527-2025</t>
+          <t>A 12110-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7850,10 +7845,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45989</v>
+        <v>45729</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7866,7 +7861,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7909,7 +7904,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54143-2025</t>
+          <t>A 15890-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7923,10 +7918,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45964</v>
+        <v>45405</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7939,7 +7934,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7982,7 +7977,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40154-2023</t>
+          <t>A 19173-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7996,10 +7991,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45169</v>
+        <v>45769</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8013,11 +8008,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8060,7 +8055,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7417-2025</t>
+          <t>A 50124-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8074,10 +8069,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45705</v>
+        <v>44860</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8090,7 +8085,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8133,7 +8128,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56940-2021</t>
+          <t>A 60339-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8147,10 +8142,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44480</v>
+        <v>45994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8162,8 +8157,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8206,7 +8206,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 73797-2021</t>
+          <t>A 54306-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44552</v>
+        <v>45232</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8235,8 +8235,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8279,7 +8284,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40232-2024</t>
+          <t>A 3354-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8293,10 +8298,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45554</v>
+        <v>45679</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8309,7 +8314,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8352,7 +8357,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62155-2025</t>
+          <t>A 57993-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8366,10 +8371,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46006</v>
+        <v>45631</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8382,7 +8387,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8425,7 +8430,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 40140-2023</t>
+          <t>A 11664-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8439,10 +8444,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45169</v>
+        <v>44992</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8454,13 +8459,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 37198-2023</t>
+          <t>A 13471-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45155</v>
+        <v>46093</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8532,13 +8532,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8581,7 +8576,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62882-2025</t>
+          <t>A 48396-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8595,10 +8590,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46008</v>
+        <v>45205</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8610,8 +8605,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8654,7 +8654,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50005-2024</t>
+          <t>A 13465-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45598</v>
+        <v>46093</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8683,13 +8683,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8732,7 +8727,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 56-2026</t>
+          <t>A 14234-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8746,10 +8741,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46014</v>
+        <v>46099</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8761,8 +8756,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>22.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46864-2023</t>
+          <t>A 45066-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45200</v>
+        <v>45191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8836,11 +8836,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 18960-2025</t>
+          <t>A 15261-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45764</v>
+        <v>46105</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8912,13 +8912,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8961,7 +8956,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29620-2025</t>
+          <t>A 15263-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8975,10 +8970,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45825</v>
+        <v>46105</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8991,7 +8986,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9034,7 +9029,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27580-2024</t>
+          <t>A 15265-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9048,10 +9043,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45474</v>
+        <v>46105</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9063,8 +9058,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20968-2026</t>
+          <t>A 15981-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9136,8 +9136,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9180,7 +9185,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30211-2025</t>
+          <t>A 16383-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9194,10 +9199,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45827</v>
+        <v>46111</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9211,11 +9216,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9258,7 +9263,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21218-2026</t>
+          <t>A 17063-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9272,10 +9277,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46146</v>
+        <v>46114</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9289,11 +9294,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>12.1</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9336,7 +9341,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21526-2026</t>
+          <t>A 16897-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9350,10 +9355,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46148</v>
+        <v>46113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9365,8 +9370,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9409,7 +9419,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21504-2026</t>
+          <t>A 49763-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9423,10 +9433,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46148</v>
+        <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9439,7 +9449,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9482,7 +9492,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22092-2026</t>
+          <t>A 17318-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9496,10 +9506,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46149</v>
+        <v>46119</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9511,8 +9521,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9555,7 +9570,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21973-2026</t>
+          <t>A 36443-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9569,10 +9584,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46153</v>
+        <v>45537</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9584,13 +9599,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9633,7 +9643,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21983-2026</t>
+          <t>A 28589-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9647,10 +9657,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46153</v>
+        <v>45103</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9660,11 +9670,6 @@
       <c r="G110" t="inlineStr">
         <is>
           <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -9711,7 +9716,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28589-2023</t>
+          <t>A 51790-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9721,14 +9726,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45103</v>
+        <v>45607</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9741,7 +9746,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9784,7 +9789,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 36443-2024</t>
+          <t>A 56940-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9794,14 +9799,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45537</v>
+        <v>44480</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9814,7 +9819,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9857,7 +9862,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56400-2025</t>
+          <t>A 40232-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9867,14 +9872,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45974</v>
+        <v>45554</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9887,7 +9892,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9930,7 +9935,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47610-2022</t>
+          <t>A 40140-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9944,10 +9949,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44852</v>
+        <v>45169</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9959,8 +9964,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10003,7 +10013,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45066-2023</t>
+          <t>A 18960-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10017,10 +10027,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45191</v>
+        <v>45764</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10034,11 +10044,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10081,7 +10091,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25540-2023</t>
+          <t>A 50005-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10095,10 +10105,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45089</v>
+        <v>45598</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10110,8 +10120,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10154,7 +10169,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 11664-2023</t>
+          <t>A 47610-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10168,10 +10183,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44992</v>
+        <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10184,7 +10199,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10227,7 +10242,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51798-2024</t>
+          <t>A 8746-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10241,10 +10256,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45607</v>
+        <v>44973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10257,7 +10272,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10300,7 +10315,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 25331-2026</t>
+          <t>A 3587-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10310,14 +10325,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46176</v>
+        <v>45320</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10329,13 +10344,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10378,7 +10388,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 47846-2024</t>
+          <t>A 23702-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10392,10 +10402,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45588</v>
+        <v>45454</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10408,7 +10418,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10451,7 +10461,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16225-2023</t>
+          <t>A 23705-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10465,10 +10475,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45028</v>
+        <v>45454</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10481,7 +10491,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10524,7 +10534,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 43103-2024</t>
+          <t>A 20968-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10534,14 +10544,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45567</v>
+        <v>46142</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10554,7 +10564,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10597,7 +10607,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27473-2026</t>
+          <t>A 19377-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10607,14 +10617,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46189</v>
+        <v>45769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10626,13 +10636,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>13.7</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10675,7 +10680,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21543-2023</t>
+          <t>A 21218-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10689,10 +10694,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45063</v>
+        <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10704,8 +10709,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2.8</v>
+        <v>12.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10748,7 +10758,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27475-2026</t>
+          <t>A 21504-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10762,10 +10772,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46189</v>
+        <v>46148</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10777,13 +10787,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10826,7 +10831,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 27716-2026</t>
+          <t>A 16629-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10840,10 +10845,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46190</v>
+        <v>45408</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10861,7 +10866,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10904,7 +10909,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 48396-2023</t>
+          <t>A 21526-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10918,10 +10923,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45205</v>
+        <v>46148</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10933,13 +10938,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10982,7 +10982,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 38018-2025</t>
+          <t>A 22092-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45882</v>
+        <v>46149</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11011,13 +11011,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>15</v>
+        <v>2.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11060,7 +11055,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 38019-2025</t>
+          <t>A 21973-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11074,10 +11069,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45882</v>
+        <v>46153</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11091,7 +11086,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -11138,7 +11133,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32524-2023</t>
+          <t>A 20381-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11152,10 +11147,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45121</v>
+        <v>45056</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11168,7 +11163,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11211,7 +11206,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 21976-2026</t>
+          <t>A 37198-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11225,10 +11220,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46153</v>
+        <v>45155</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11242,11 +11237,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11289,7 +11284,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11099-2022</t>
+          <t>A 20378-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11299,14 +11294,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44628</v>
+        <v>45056</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11319,7 +11314,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11362,7 +11357,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21232-2024</t>
+          <t>A 59705-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11376,10 +11371,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45440</v>
+        <v>45639</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11392,7 +11387,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11435,7 +11430,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46045-2023</t>
+          <t>A 27580-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11449,10 +11444,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45196</v>
+        <v>45474</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11464,13 +11459,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11513,7 +11503,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34832-2026</t>
+          <t>A 47753-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11527,10 +11517,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46258</v>
+        <v>45588</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11542,13 +11532,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11591,7 +11576,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 54306-2023</t>
+          <t>A 56400-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11601,14 +11586,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45232</v>
+        <v>45974</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11620,13 +11605,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11669,7 +11649,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 59705-2024</t>
+          <t>A 7744-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11683,10 +11663,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45639</v>
+        <v>44973</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11698,8 +11678,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11742,7 +11727,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 16503-2024</t>
+          <t>A 17075-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11756,10 +11741,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45408</v>
+        <v>45034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11773,11 +11758,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11820,7 +11805,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 6388-2025</t>
+          <t>A 25331-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11834,10 +11819,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45699</v>
+        <v>46176</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11849,8 +11834,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11893,7 +11883,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 40153-2023</t>
+          <t>A 37011-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11907,10 +11897,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45169</v>
+        <v>45155</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11924,11 +11914,11 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11971,7 +11961,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37011-2023</t>
+          <t>A 27589-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11985,10 +11975,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45155</v>
+        <v>45474</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12000,13 +11990,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12049,7 +12034,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35726-2026</t>
+          <t>A 53224-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12063,10 +12048,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46265</v>
+        <v>45613</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12078,13 +12063,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12127,7 +12107,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 31483-2026</t>
+          <t>A 27473-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12141,10 +12121,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46223</v>
+        <v>46189</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12156,8 +12136,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>9.800000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12200,7 +12185,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3354-2025</t>
+          <t>A 27475-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12214,10 +12199,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45679</v>
+        <v>46189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12229,8 +12214,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12273,7 +12263,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35731-2026</t>
+          <t>A 27716-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12287,10 +12277,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46265</v>
+        <v>46190</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12308,7 +12298,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12351,7 +12341,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 36394-2026</t>
+          <t>A 16503-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12365,10 +12355,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46268</v>
+        <v>45408</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12386,7 +12376,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>8.9</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12429,7 +12419,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36389-2026</t>
+          <t>A 40153-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12443,10 +12433,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46268</v>
+        <v>45169</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12464,7 +12454,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12507,7 +12497,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53030-2023</t>
+          <t>A 41448-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12521,10 +12511,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45226</v>
+        <v>45560</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12538,11 +12528,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12585,7 +12575,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 12526-2025</t>
+          <t>A 21976-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12599,10 +12589,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45730</v>
+        <v>46153</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12614,8 +12604,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12658,7 +12653,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 19254-2023</t>
+          <t>A 46865-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12672,10 +12667,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45049</v>
+        <v>45200</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12687,8 +12682,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12731,7 +12731,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28607-2026</t>
+          <t>A 19164-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12745,10 +12745,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46197</v>
+        <v>45769</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12762,11 +12762,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12809,7 +12809,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 28608-2026</t>
+          <t>A 25540-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12823,10 +12823,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46197</v>
+        <v>45089</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12838,13 +12838,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12887,7 +12882,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 34232-2026</t>
+          <t>A 47846-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12901,10 +12896,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46253</v>
+        <v>45588</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12917,7 +12912,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12960,7 +12955,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 31967-2026</t>
+          <t>A 58616-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12970,14 +12965,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46232</v>
+        <v>45632</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12995,7 +12990,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13038,7 +13033,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 31972-2026</t>
+          <t>A 21543-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13052,10 +13047,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46232</v>
+        <v>45063</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13068,7 +13063,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13111,7 +13106,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32062-2026</t>
+          <t>A 51793-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13125,10 +13120,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46233</v>
+        <v>45607</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13140,13 +13135,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>8.199999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13189,7 +13179,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 57990-2024</t>
+          <t>A 19254-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13203,10 +13193,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45631</v>
+        <v>45049</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13219,7 +13209,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13262,7 +13252,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 63505-2023</t>
+          <t>A 67356-2021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13272,14 +13262,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45274</v>
+        <v>44523</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13292,7 +13282,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13335,7 +13325,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 32385-2026</t>
+          <t>A 16042-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13345,14 +13335,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46238</v>
+        <v>45405</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13365,7 +13355,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>7.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13408,7 +13398,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 19164-2025</t>
+          <t>A 34832-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13422,10 +13412,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45769</v>
+        <v>46258</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13439,11 +13429,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13486,7 +13476,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 19173-2025</t>
+          <t>A 54573-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13500,10 +13490,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45769</v>
+        <v>45233</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13517,11 +13507,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13564,7 +13554,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 12796-2023</t>
+          <t>A 35731-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13578,10 +13568,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45001</v>
+        <v>46265</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13593,8 +13583,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>22.4</v>
+        <v>3.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13637,7 +13632,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 33483-2026</t>
+          <t>A 32524-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13651,10 +13646,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46246</v>
+        <v>45121</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13667,7 +13662,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13710,7 +13705,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 47029-2024</t>
+          <t>A 35726-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13724,10 +13719,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45586</v>
+        <v>46265</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13739,8 +13734,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13783,7 +13783,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36013-2026</t>
+          <t>A 16225-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13797,10 +13797,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46266</v>
+        <v>45028</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13812,13 +13812,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13861,7 +13856,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 51778-2024</t>
+          <t>A 31483-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13875,10 +13870,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45607</v>
+        <v>46223</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13891,7 +13886,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13934,7 +13929,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 46865-2023</t>
+          <t>A 25477-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13948,10 +13943,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45200</v>
+        <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13963,13 +13958,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14012,7 +14002,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 33443-2026</t>
+          <t>A 36389-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14026,10 +14016,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46247</v>
+        <v>46268</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14047,7 +14037,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14090,7 +14080,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 41448-2024</t>
+          <t>A 43073-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14104,10 +14094,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45560</v>
+        <v>45567</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14119,13 +14109,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14168,7 +14153,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 20381-2023</t>
+          <t>A 36394-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14182,10 +14167,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45056</v>
+        <v>46268</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14197,8 +14182,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14241,7 +14231,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 54573-2023</t>
+          <t>A 24540-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14255,10 +14245,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45233</v>
+        <v>44727</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14272,11 +14262,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14319,7 +14309,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23702-2024</t>
+          <t>A 28607-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14333,10 +14323,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45454</v>
+        <v>46197</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14348,8 +14338,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14392,7 +14387,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 23705-2024</t>
+          <t>A 28608-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14406,10 +14401,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45454</v>
+        <v>46197</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14421,8 +14416,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14465,7 +14465,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 24540-2022</t>
+          <t>A 34232-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44727</v>
+        <v>46253</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14494,13 +14494,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14543,7 +14538,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 47753-2024</t>
+          <t>A 51798-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14557,10 +14552,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45588</v>
+        <v>45607</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14573,7 +14568,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14616,7 +14611,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 42198-2023</t>
+          <t>A 31972-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14630,10 +14625,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45179</v>
+        <v>46232</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14645,13 +14640,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14694,7 +14684,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 51790-2024</t>
+          <t>A 11099-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14704,14 +14694,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45607</v>
+        <v>44992</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14724,7 +14714,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14767,7 +14757,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 19377-2025</t>
+          <t>A 40144-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14777,14 +14767,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45769</v>
+        <v>45169</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14796,8 +14786,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14840,7 +14835,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 3131-2024</t>
+          <t>A 31967-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14850,14 +14845,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45316</v>
+        <v>46232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14869,8 +14864,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14913,7 +14913,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 43073-2024</t>
+          <t>A 40154-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14927,10 +14927,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45567</v>
+        <v>45169</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14942,8 +14942,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14986,7 +14991,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 58616-2024</t>
+          <t>A 32062-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15000,10 +15005,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45632</v>
+        <v>46233</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15017,11 +15022,11 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15064,7 +15069,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 19075-2022</t>
+          <t>A 21232-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15078,10 +15083,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44691</v>
+        <v>45440</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15093,13 +15098,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15142,7 +15142,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12110-2025</t>
+          <t>A 32385-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15152,14 +15152,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45729</v>
+        <v>46238</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15215,7 +15215,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 49763-2024</t>
+          <t>A 45065-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15229,10 +15229,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45597</v>
+        <v>45191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15244,8 +15244,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15288,7 +15293,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 17075-2023</t>
+          <t>A 46041-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15302,10 +15307,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45034</v>
+        <v>45196</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15323,7 +15328,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15366,7 +15371,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 11099-2023</t>
+          <t>A 13654-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15380,10 +15385,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44992</v>
+        <v>45390</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15396,7 +15401,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15439,7 +15444,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 45065-2023</t>
+          <t>A 33483-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15453,10 +15458,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45191</v>
+        <v>46246</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15468,13 +15473,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15517,7 +15517,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 46041-2023</t>
+          <t>A 47029-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45196</v>
+        <v>45586</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15546,13 +15546,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15595,7 +15590,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 13654-2024</t>
+          <t>A 36013-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15609,10 +15604,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45390</v>
+        <v>46266</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15624,8 +15619,13 @@
           <t>NORBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15668,7 +15668,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 23418-2025</t>
+          <t>A 33443-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45792</v>
+        <v>46247</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15699,11 +15699,11 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15746,24 +15746,24 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23433-2025</t>
+          <t>S 409-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45792</v>
+        <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15777,11 +15777,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>6.2</v>
+        <v>10.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15824,7 +15824,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S 409-2022</t>
+          <t>S 606-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15838,10 +15838,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44585</v>
+        <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>10.9</v>
+        <v>26.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15899,10 +15899,10 @@
       </c>
       <c r="V192" s="2" t="inlineStr"/>
     </row>
-    <row r="193" ht="15" customHeight="1">
+    <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S 606-2026</t>
+          <t>S 2097-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15912,14 +15912,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46085</v>
+        <v>46238</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15931,13 +15931,8 @@
           <t>NORBERG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>26.4</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15976,79 +15971,6 @@
         <v>0</v>
       </c>
       <c r="V193" s="2" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>S 2097-2026</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D194" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E194" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I194" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J194" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" t="n">
-        <v>0</v>
-      </c>
-      <c r="O194" t="n">
-        <v>0</v>
-      </c>
-      <c r="P194" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="n">
-        <v>0</v>
-      </c>
-      <c r="T194" t="n">
-        <v>0</v>
-      </c>
-      <c r="U194" t="n">
-        <v>0</v>
-      </c>
-      <c r="V194" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NORBERG.xlsx
+++ b/Översikt NORBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46042</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46247</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45268</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>45420</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 15262-2026</t>
+          <t>A 55711-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46105</v>
+        <v>45622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1218,376 +1218,376 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Persiljespindling
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 15262-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Brunklöver
 Tvåblad</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 15262-2026 artfynd.xlsx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 15262-2026 karta.png", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 15262-2026 georefererad karta.tif", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 15262-2026 FSC-klagomål.docx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 15262-2026 FSC-klagomål mail.docx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 15262-2026 tillsynsbegäran.docx", "A 15262-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 15262-2026 tillsynsbegäran mail.docx", "A 15262-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 63777-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46019</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 26072-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45091</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>3.4</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>8</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>8</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 26072-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45091</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63777-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>8</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>8</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 26072-2023 artfynd.xlsx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 26072-2023 karta.png", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 26072-2023 georefererad karta.tif", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 26072-2023 FSC-klagomål.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 26072-2023 FSC-klagomål mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 26072-2023 tillsynsbegäran.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 26072-2023 tillsynsbegäran mail.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 26072-2023 prioriterade fågelarter.docx", "A 26072-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 55711-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45622</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Persiljespindling
-Skogsknipprot</t>
-        </is>
-      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 55711-2024 artfynd.xlsx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 63777-2025 artfynd.xlsx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 55711-2024 karta.png", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 63777-2025 karta.png", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 55711-2024 georefererad karta.tif", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 63777-2025 georefererad karta.tif", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 55711-2024 FSC-klagomål.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 63777-2025 FSC-klagomål.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 55711-2024 FSC-klagomål mail.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 63777-2025 FSC-klagomål mail.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 55711-2024 tillsynsbegäran.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 63777-2025 tillsynsbegäran.docx", "A 63777-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 55711-2024 tillsynsbegäran mail.docx", "A 55711-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 63777-2025 tillsynsbegäran mail.docx", "A 63777-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/fåglar/A 63777-2025 prioriterade fågelarter.docx", "A 63777-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33377-2023</t>
+          <t>A 36009-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45128</v>
+        <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1658,151 +1658,151 @@
         <v>2</v>
       </c>
       <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 36009-2026 artfynd.xlsx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 36009-2026 karta.png", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 36009-2026 georefererad karta.tif", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 36009-2026 FSC-klagomål.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 36009-2026 FSC-klagomål mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 36009-2026 tillsynsbegäran.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 36009-2026 tillsynsbegäran mail.docx", "A 36009-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 33377-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45128</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NORBERG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Gul taggsvamp
 Dofttaggsvamp</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/artfynd/A 33377-2023 artfynd.xlsx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor/A 33377-2023 karta.png", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/kartor_geotiff/A 33377-2023 georefererad karta.tif", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomål/A 33377-2023 FSC-klagomål.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/klagomålsmail/A 33377-2023 FSC-klagomål mail.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsyn/A 33377-2023 tillsynsbegäran.docx", "A 33377-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1962/tillsynsmail/A 33377-2023 tillsynsbegäran mail.docx", "A 33377-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 36009-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NORBERG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
- 